--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{293EA8A2-40F3-4785-90C0-1DDE4E5BB377}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611233A3-A543-4374-86BB-65352107C324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25710" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11055" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,54 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="282">
   <si>
-    <t>人物</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>语音</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景/cg</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>背景音乐</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>转场特效</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>立绘</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>对话框头像</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>#TAG</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>选项</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>QTE</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>指令</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1171,12 +1123,48 @@
     <t>音乐/Airport Lounge</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>人物</t>
+  </si>
+  <si>
+    <t>对话</t>
+  </si>
+  <si>
+    <t>语音</t>
+  </si>
+  <si>
+    <t>背景/cg</t>
+  </si>
+  <si>
+    <t>背景音乐</t>
+  </si>
+  <si>
+    <t>转场特效</t>
+  </si>
+  <si>
+    <t>立绘层</t>
+  </si>
+  <si>
+    <t>对话框头像</t>
+  </si>
+  <si>
+    <t>#TAG</t>
+  </si>
+  <si>
+    <t>选项</t>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
+  </si>
+  <si>
+    <t>指令</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1205,13 +1193,6 @@
       <sz val="9"/>
       <name val="等线"/>
       <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="等线"/>
-      <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1269,7 +1250,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1628,99 +1609,100 @@
     <col min="2" max="2" width="56.25" customWidth="1"/>
     <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="10" max="10" width="37.25" customWidth="1"/>
+    <col min="11" max="11" width="35.625" customWidth="1"/>
     <col min="12" max="12" width="17.375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>1</v>
+        <v>271</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>2</v>
+        <v>272</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>3</v>
+        <v>273</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>4</v>
+        <v>274</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>5</v>
+        <v>275</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>6</v>
+        <v>276</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>7</v>
+        <v>277</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>8</v>
+        <v>278</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>9</v>
+        <v>279</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>10</v>
+        <v>280</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>11</v>
+        <v>281</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D3" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F3" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D4" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -1729,1847 +1711,1847 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>13</v>
+        <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="D11" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="D12" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E12" t="s">
-        <v>256</v>
+        <v>244</v>
       </c>
       <c r="F12" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="D13" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="E13" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="F13" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="D14" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F14" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B15" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="D15" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D16" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="F16" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>266</v>
+        <v>254</v>
       </c>
       <c r="C17" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="D17" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="L17" t="s">
-        <v>273</v>
+        <v>261</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B18" t="s">
-        <v>180</v>
+        <v>168</v>
       </c>
       <c r="D18" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="F18" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>181</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>270</v>
+        <v>258</v>
       </c>
       <c r="D20" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="F20" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>182</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D21" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F21" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B22" t="s">
-        <v>271</v>
+        <v>259</v>
       </c>
       <c r="C22" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D22" t="s">
-        <v>257</v>
+        <v>245</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="L22" t="s">
-        <v>272</v>
+        <v>260</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="C23" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="D23" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F23" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B25" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C26" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B27" t="s">
-        <v>269</v>
+        <v>257</v>
       </c>
       <c r="G27" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="L27" t="s">
-        <v>268</v>
+        <v>256</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>183</v>
+        <v>171</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="G28" t="s">
-        <v>243</v>
+        <v>231</v>
       </c>
       <c r="L28" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B29" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A31" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B32" t="s">
-        <v>186</v>
+        <v>174</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B33" t="s">
-        <v>21</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B34" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B35" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B36" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B39" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>190</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="B44" t="s">
-        <v>27</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="D46" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="E46" t="s">
-        <v>255</v>
+        <v>243</v>
       </c>
       <c r="G46" t="s">
-        <v>259</v>
+        <v>247</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="C47" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="D47" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F47" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G47" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="E48" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="C49" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="D49" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E49" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F49" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>260</v>
+        <v>248</v>
       </c>
       <c r="D50" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="G50" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>128</v>
+        <v>116</v>
       </c>
       <c r="D51" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="E51" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F51" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G51" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>130</v>
+        <v>118</v>
       </c>
       <c r="I52" t="s">
-        <v>136</v>
+        <v>124</v>
       </c>
       <c r="J52" t="s">
-        <v>135</v>
+        <v>123</v>
       </c>
       <c r="L52" t="s">
-        <v>140</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
-        <v>133</v>
+        <v>121</v>
       </c>
       <c r="E54" t="s">
-        <v>275</v>
+        <v>263</v>
       </c>
       <c r="I54" t="s">
-        <v>134</v>
+        <v>122</v>
       </c>
       <c r="L54" t="s">
-        <v>192</v>
+        <v>180</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B55" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="C55" t="s">
-        <v>129</v>
+        <v>117</v>
       </c>
       <c r="I55" t="s">
-        <v>132</v>
+        <v>120</v>
       </c>
       <c r="L55" t="s">
-        <v>139</v>
+        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>207</v>
+        <v>195</v>
       </c>
       <c r="E57" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="I57" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="L57" t="s">
-        <v>138</v>
+        <v>126</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>28</v>
+        <v>16</v>
       </c>
       <c r="C58" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="G58" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B59" t="s">
-        <v>246</v>
+        <v>234</v>
       </c>
       <c r="G59" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B60" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B61" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>195</v>
+        <v>183</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>196</v>
+        <v>184</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>197</v>
+        <v>185</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>198</v>
+        <v>186</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>127</v>
+        <v>115</v>
       </c>
       <c r="I66" t="s">
-        <v>205</v>
+        <v>193</v>
       </c>
       <c r="J66" t="s">
-        <v>201</v>
+        <v>189</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>202</v>
+        <v>190</v>
       </c>
       <c r="I67" t="s">
-        <v>199</v>
+        <v>187</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>203</v>
+        <v>191</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>29</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D70" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="F70" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="I70" t="s">
-        <v>200</v>
+        <v>188</v>
       </c>
       <c r="L70" t="s">
-        <v>206</v>
+        <v>194</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>208</v>
+        <v>196</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A72" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>209</v>
+        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>210</v>
+        <v>198</v>
       </c>
       <c r="G73" t="s">
-        <v>276</v>
+        <v>264</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>211</v>
+        <v>199</v>
       </c>
       <c r="D74" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="G74" t="s">
-        <v>277</v>
+        <v>265</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="D75" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F75" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G75" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A77" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>213</v>
+        <v>201</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C78" t="s">
-        <v>145</v>
+        <v>133</v>
       </c>
       <c r="L78" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>214</v>
+        <v>202</v>
       </c>
       <c r="D79" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G79" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="L79" t="s">
-        <v>279</v>
+        <v>267</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A80" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
       <c r="C80" t="s">
-        <v>147</v>
+        <v>135</v>
       </c>
       <c r="D80" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F80" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G80" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
       <c r="L80" t="s">
-        <v>278</v>
+        <v>266</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>30</v>
+        <v>18</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="B82" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B83" t="s">
-        <v>33</v>
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B84" t="s">
-        <v>217</v>
+        <v>205</v>
       </c>
       <c r="D84" t="s">
-        <v>146</v>
+        <v>134</v>
       </c>
       <c r="F84" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G84" t="s">
-        <v>248</v>
+        <v>236</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
       <c r="D85" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="F85" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="G85" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>35</v>
+        <v>23</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>219</v>
+        <v>207</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>36</v>
+        <v>24</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B89" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>220</v>
+        <v>208</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>221</v>
+        <v>209</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="D92" t="s">
-        <v>144</v>
+        <v>132</v>
       </c>
       <c r="G92" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="L92" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B93" t="s">
-        <v>148</v>
+        <v>136</v>
       </c>
       <c r="D93" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="F93" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G93" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="L93" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D94" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
       <c r="F94" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A95" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="C95" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="L95" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="96" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>39</v>
+        <v>27</v>
       </c>
       <c r="B96" s="7" t="s">
-        <v>40</v>
+        <v>28</v>
       </c>
       <c r="L96" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B97" t="s">
-        <v>152</v>
+        <v>140</v>
       </c>
       <c r="L97" t="s">
-        <v>143</v>
+        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C98" t="s">
-        <v>151</v>
+        <v>139</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B99" t="s">
-        <v>153</v>
+        <v>141</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B100" t="s">
-        <v>223</v>
+        <v>211</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B101" t="s">
-        <v>41</v>
+        <v>29</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B102" t="s">
-        <v>224</v>
+        <v>212</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B103" t="s">
-        <v>225</v>
+        <v>213</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B104" t="s">
-        <v>226</v>
+        <v>214</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B105" t="s">
-        <v>43</v>
+        <v>31</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>42</v>
+        <v>30</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>44</v>
+        <v>32</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>45</v>
+        <v>33</v>
       </c>
       <c r="D108" t="s">
-        <v>150</v>
+        <v>138</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B109" t="s">
-        <v>227</v>
+        <v>215</v>
       </c>
       <c r="D109" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E109" t="s">
-        <v>274</v>
+        <v>262</v>
       </c>
       <c r="F109" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A110" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B110" t="s">
-        <v>228</v>
+        <v>216</v>
       </c>
       <c r="C110" t="s">
-        <v>154</v>
+        <v>142</v>
       </c>
       <c r="D110" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="E110" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
       <c r="F110" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="L110" t="s">
-        <v>261</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B111" t="s">
-        <v>264</v>
+        <v>252</v>
       </c>
       <c r="D111" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B112" t="s">
-        <v>156</v>
+        <v>144</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B113" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B114" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A115" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>229</v>
+        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B116" t="s">
-        <v>263</v>
+        <v>251</v>
       </c>
       <c r="D116" t="s">
-        <v>155</v>
+        <v>143</v>
       </c>
       <c r="E116" t="s">
-        <v>258</v>
+        <v>246</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>48</v>
+        <v>36</v>
       </c>
       <c r="D117" t="s">
-        <v>157</v>
+        <v>145</v>
       </c>
       <c r="E117" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="F117" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D118" t="s">
-        <v>158</v>
+        <v>146</v>
       </c>
       <c r="F118" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="C119" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="D119" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="F119" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>49</v>
+        <v>37</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B121" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B123" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>53</v>
+        <v>41</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B125" t="s">
-        <v>230</v>
+        <v>218</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>54</v>
+        <v>42</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B127" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C127" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>57</v>
+        <v>45</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B130" t="s">
-        <v>58</v>
+        <v>46</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B131" t="s">
-        <v>59</v>
+        <v>47</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B132" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B133" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C133" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B134" t="s">
-        <v>267</v>
+        <v>255</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B136" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B137" t="s">
-        <v>262</v>
+        <v>250</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>265</v>
+        <v>253</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="C139" t="s">
-        <v>163</v>
+        <v>151</v>
       </c>
       <c r="F139" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B140" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B141" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B143" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B144" t="s">
-        <v>232</v>
+        <v>220</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B145" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A146" s="3" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B147" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="D147" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="E147" t="s">
-        <v>280</v>
+        <v>268</v>
       </c>
       <c r="G147" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="L147" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="D148" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E148" t="s">
-        <v>281</v>
+        <v>269</v>
       </c>
       <c r="F148" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G148" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="L148" t="s">
-        <v>244</v>
+        <v>232</v>
       </c>
     </row>
     <row r="149" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B149" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G149" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B150" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="C150" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="G150" t="s">
-        <v>250</v>
+        <v>238</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B151" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>74</v>
+        <v>62</v>
       </c>
       <c r="C152" t="s">
-        <v>161</v>
+        <v>149</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B153" t="s">
-        <v>75</v>
+        <v>63</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B154" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B155" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B156" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B157" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B158" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B159" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="G159" t="s">
-        <v>249</v>
+        <v>237</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B160" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="G160" t="s">
-        <v>251</v>
+        <v>239</v>
       </c>
     </row>
     <row r="161" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A161" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B161" t="s">
-        <v>234</v>
+        <v>222</v>
       </c>
     </row>
     <row r="162" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A162" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B162" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C162" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
     </row>
     <row r="163" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A163" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B163" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
     </row>
     <row r="164" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A164" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B164" t="s">
-        <v>235</v>
+        <v>223</v>
       </c>
     </row>
     <row r="165" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A165" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B165" t="s">
         <v>73</v>
-      </c>
-      <c r="B165" t="s">
-        <v>85</v>
       </c>
     </row>
     <row r="166" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A166" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B166" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
     </row>
     <row r="167" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A167" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B167" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
     </row>
     <row r="168" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B168" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
     </row>
     <row r="169" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B169" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
     </row>
     <row r="170" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A170" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B170" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
     </row>
     <row r="171" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B171" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
     </row>
     <row r="172" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B172" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
     </row>
     <row r="173" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B173" t="s">
-        <v>236</v>
+        <v>224</v>
       </c>
     </row>
     <row r="174" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A174" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B174" t="s">
-        <v>237</v>
+        <v>225</v>
       </c>
     </row>
     <row r="175" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B175" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
     </row>
     <row r="176" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="B177" t="s">
-        <v>238</v>
+        <v>226</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B178" t="s">
-        <v>252</v>
+        <v>240</v>
       </c>
       <c r="C178" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D178" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
     </row>
     <row r="179" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B179" t="s">
-        <v>253</v>
+        <v>241</v>
       </c>
       <c r="G179" t="s">
-        <v>254</v>
+        <v>242</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B180" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="D180" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F180" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="G180" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
-        <v>239</v>
+        <v>227</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
-        <v>240</v>
+        <v>228</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
-        <v>241</v>
+        <v>229</v>
       </c>
       <c r="D183" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>242</v>
+        <v>230</v>
       </c>
       <c r="L184" t="s">
-        <v>245</v>
+        <v>233</v>
       </c>
     </row>
     <row r="185" spans="1:12" x14ac:dyDescent="0.2">
       <c r="L185" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{611233A3-A543-4374-86BB-65352107C324}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442B30C7-4153-41AF-BD2D-17DAC86E5406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11055" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="283">
   <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1158,6 +1158,10 @@
   </si>
   <si>
     <t>指令</t>
+  </si>
+  <si>
+    <t>播放立绘动画 &gt;&gt; A_MovedOver_Hit_B 0 1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1602,7 +1606,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF46EA-649E-46D2-A2F1-55ADFE170F2E}">
-  <dimension ref="A1:L185"/>
+  <dimension ref="A1:L186"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -2338,153 +2342,156 @@
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B63" t="s">
-        <v>184</v>
+        <v>183</v>
+      </c>
+      <c r="L63" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B64" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B66" t="s">
-        <v>6</v>
-      </c>
-      <c r="D66" t="s">
-        <v>115</v>
-      </c>
-      <c r="I66" t="s">
-        <v>193</v>
-      </c>
-      <c r="J66" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>190</v>
+        <v>6</v>
+      </c>
+      <c r="D67" t="s">
+        <v>115</v>
       </c>
       <c r="I67" t="s">
-        <v>187</v>
+        <v>193</v>
+      </c>
+      <c r="J67" t="s">
+        <v>189</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B68" t="s">
-        <v>191</v>
+        <v>190</v>
+      </c>
+      <c r="I68" t="s">
+        <v>187</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B69" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B70" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A71" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B71" t="s">
         <v>17</v>
       </c>
-      <c r="C70" t="s">
+      <c r="C71" t="s">
         <v>102</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D71" t="s">
         <v>129</v>
       </c>
-      <c r="F70" t="s">
+      <c r="F71" t="s">
         <v>87</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I71" t="s">
         <v>188</v>
       </c>
-      <c r="L70" t="s">
+      <c r="L71" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B71" t="s">
+    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B72" t="s">
         <v>196</v>
-      </c>
-    </row>
-    <row r="72" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A72" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B72" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B73" t="s">
-        <v>198</v>
-      </c>
-      <c r="G73" t="s">
-        <v>264</v>
+        <v>197</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B74" t="s">
-        <v>199</v>
-      </c>
-      <c r="D74" t="s">
-        <v>129</v>
+        <v>198</v>
       </c>
       <c r="G74" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>91</v>
+        <v>8</v>
+      </c>
+      <c r="B75" t="s">
+        <v>199</v>
       </c>
       <c r="D75" t="s">
-        <v>132</v>
-      </c>
-      <c r="F75" t="s">
-        <v>87</v>
+        <v>129</v>
       </c>
       <c r="G75" t="s">
-        <v>2</v>
+        <v>265</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B76" t="s">
-        <v>200</v>
+        <v>91</v>
+      </c>
+      <c r="D76" t="s">
+        <v>132</v>
+      </c>
+      <c r="F76" t="s">
+        <v>87</v>
+      </c>
+      <c r="G76" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -2492,38 +2499,29 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B78" t="s">
-        <v>203</v>
-      </c>
-      <c r="C78" t="s">
-        <v>133</v>
-      </c>
-      <c r="L78" t="s">
-        <v>266</v>
+        <v>201</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B79" t="s">
-        <v>202</v>
-      </c>
-      <c r="D79" t="s">
-        <v>132</v>
-      </c>
-      <c r="G79" t="s">
-        <v>2</v>
+        <v>203</v>
+      </c>
+      <c r="C79" t="s">
+        <v>133</v>
       </c>
       <c r="L79" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -2531,408 +2529,408 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>204</v>
-      </c>
-      <c r="C80" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="D80" t="s">
-        <v>134</v>
-      </c>
-      <c r="F80" t="s">
-        <v>92</v>
+        <v>132</v>
       </c>
       <c r="G80" t="s">
-        <v>236</v>
+        <v>2</v>
       </c>
       <c r="L80" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B81" t="s">
-        <v>18</v>
+        <v>204</v>
+      </c>
+      <c r="C81" t="s">
+        <v>135</v>
+      </c>
+      <c r="D81" t="s">
+        <v>134</v>
+      </c>
+      <c r="F81" t="s">
+        <v>92</v>
+      </c>
+      <c r="G81" t="s">
+        <v>236</v>
+      </c>
+      <c r="L81" t="s">
+        <v>266</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="B82" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="B83" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B84" t="s">
-        <v>205</v>
-      </c>
-      <c r="D84" t="s">
-        <v>134</v>
-      </c>
-      <c r="F84" t="s">
-        <v>92</v>
-      </c>
-      <c r="G84" t="s">
-        <v>236</v>
+        <v>21</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="B85" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D85" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="F85" t="s">
         <v>92</v>
       </c>
       <c r="G85" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B86" t="s">
-        <v>23</v>
+        <v>206</v>
+      </c>
+      <c r="D86" t="s">
+        <v>132</v>
+      </c>
+      <c r="F86" t="s">
+        <v>92</v>
+      </c>
+      <c r="G86" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B87" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B88" t="s">
-        <v>24</v>
+        <v>207</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B89" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B90" t="s">
-        <v>208</v>
+        <v>25</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B91" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B92" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A93" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B93" t="s">
         <v>210</v>
       </c>
-      <c r="D92" t="s">
+      <c r="D93" t="s">
         <v>132</v>
       </c>
-      <c r="G92" t="s">
+      <c r="G93" t="s">
         <v>235</v>
       </c>
-      <c r="L92" t="s">
+      <c r="L93" t="s">
         <v>232</v>
-      </c>
-    </row>
-    <row r="93" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B93" t="s">
-        <v>136</v>
-      </c>
-      <c r="D93" t="s">
-        <v>88</v>
-      </c>
-      <c r="F93" t="s">
-        <v>87</v>
-      </c>
-      <c r="G93" t="s">
-        <v>86</v>
-      </c>
-      <c r="L93" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B94" t="s">
+        <v>136</v>
+      </c>
+      <c r="D94" t="s">
+        <v>88</v>
+      </c>
+      <c r="F94" t="s">
+        <v>87</v>
+      </c>
+      <c r="G94" t="s">
+        <v>86</v>
+      </c>
+      <c r="L94" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B95" t="s">
         <v>137</v>
       </c>
-      <c r="D94" t="s">
+      <c r="D95" t="s">
         <v>138</v>
       </c>
-      <c r="F94" t="s">
+      <c r="F95" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A95" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B95" t="s">
+    <row r="96" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A96" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B96" t="s">
         <v>26</v>
       </c>
-      <c r="C95" t="s">
+      <c r="C96" t="s">
         <v>109</v>
       </c>
-      <c r="L95" t="s">
+      <c r="L96" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="96" spans="1:12" ht="171" x14ac:dyDescent="0.2">
-      <c r="A96" s="3" t="s">
+    <row r="97" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+      <c r="A97" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B96" s="7" t="s">
+      <c r="B97" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="L96" t="s">
+      <c r="L97" t="s">
         <v>130</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A97" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B97" t="s">
-        <v>140</v>
-      </c>
-      <c r="L97" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A98" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C98" t="s">
-        <v>139</v>
+        <v>0</v>
+      </c>
+      <c r="B98" t="s">
+        <v>140</v>
+      </c>
+      <c r="L98" t="s">
+        <v>131</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B99" t="s">
-        <v>141</v>
+        <v>91</v>
+      </c>
+      <c r="C99" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A100" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>211</v>
+        <v>141</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A101" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B101" t="s">
-        <v>29</v>
+        <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A102" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B102" t="s">
-        <v>212</v>
+        <v>29</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B103" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B104" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B105" t="s">
-        <v>31</v>
+        <v>214</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B106" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B107" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B108" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A109" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B109" t="s">
         <v>33</v>
       </c>
-      <c r="D108" t="s">
+      <c r="D109" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="109" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B109" t="s">
+    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B110" t="s">
         <v>215</v>
-      </c>
-      <c r="D109" t="s">
-        <v>88</v>
-      </c>
-      <c r="E109" t="s">
-        <v>262</v>
-      </c>
-      <c r="F109" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="110" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A110" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B110" t="s">
-        <v>216</v>
-      </c>
-      <c r="C110" t="s">
-        <v>142</v>
       </c>
       <c r="D110" t="s">
         <v>88</v>
       </c>
       <c r="E110" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="F110" t="s">
         <v>87</v>
       </c>
-      <c r="L110" t="s">
-        <v>249</v>
-      </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B111" t="s">
-        <v>252</v>
+        <v>216</v>
+      </c>
+      <c r="C111" t="s">
+        <v>142</v>
       </c>
       <c r="D111" t="s">
-        <v>143</v>
+        <v>88</v>
+      </c>
+      <c r="E111" t="s">
+        <v>246</v>
+      </c>
+      <c r="F111" t="s">
+        <v>87</v>
+      </c>
+      <c r="L111" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A112" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>144</v>
+        <v>252</v>
+      </c>
+      <c r="D112" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B113" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B114" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B114" t="s">
+    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B115" t="s">
         <v>35</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A115" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B115" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A116" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B116" t="s">
-        <v>251</v>
-      </c>
-      <c r="D116" t="s">
-        <v>143</v>
-      </c>
-      <c r="E116" t="s">
-        <v>246</v>
+        <v>217</v>
       </c>
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B117" t="s">
-        <v>36</v>
+        <v>251</v>
       </c>
       <c r="D117" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="E117" t="s">
-        <v>268</v>
-      </c>
-      <c r="F117" t="s">
-        <v>87</v>
+        <v>246</v>
       </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.2">
@@ -2940,24 +2938,27 @@
         <v>0</v>
       </c>
       <c r="B118" t="s">
-        <v>147</v>
+        <v>36</v>
       </c>
       <c r="D118" t="s">
-        <v>146</v>
+        <v>145</v>
+      </c>
+      <c r="E118" t="s">
+        <v>268</v>
       </c>
       <c r="F118" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A119" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C119" t="s">
-        <v>102</v>
+        <v>0</v>
+      </c>
+      <c r="B119" t="s">
+        <v>147</v>
       </c>
       <c r="D119" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F119" t="s">
         <v>92</v>
@@ -2965,136 +2966,142 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B120" t="s">
-        <v>37</v>
+        <v>91</v>
+      </c>
+      <c r="C120" t="s">
+        <v>102</v>
+      </c>
+      <c r="D120" t="s">
+        <v>148</v>
+      </c>
+      <c r="F120" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B121" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A122" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B122" t="s">
-        <v>219</v>
+        <v>38</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>40</v>
+        <v>219</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B124" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>218</v>
+        <v>41</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>42</v>
+        <v>218</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B127" t="s">
-        <v>43</v>
-      </c>
-      <c r="C127" t="s">
-        <v>149</v>
+        <v>42</v>
       </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B128" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="C128" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B130" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B131" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B132" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B133" t="s">
-        <v>49</v>
-      </c>
-      <c r="C133" t="s">
-        <v>150</v>
+        <v>48</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A134" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B134" t="s">
-        <v>255</v>
+        <v>49</v>
+      </c>
+      <c r="C134" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B135" t="s">
-        <v>50</v>
+        <v>255</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
@@ -3102,23 +3109,23 @@
         <v>2</v>
       </c>
       <c r="B136" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B137" t="s">
-        <v>250</v>
+        <v>51</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>0</v>
+        <v>39</v>
       </c>
       <c r="B138" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
@@ -3126,61 +3133,61 @@
         <v>0</v>
       </c>
       <c r="B139" t="s">
-        <v>55</v>
-      </c>
-      <c r="C139" t="s">
-        <v>151</v>
-      </c>
-      <c r="F139" t="s">
-        <v>87</v>
+        <v>253</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B140" t="s">
-        <v>52</v>
+        <v>55</v>
+      </c>
+      <c r="C140" t="s">
+        <v>151</v>
+      </c>
+      <c r="F140" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B141" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B142" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B143" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B144" t="s">
-        <v>220</v>
+        <v>54</v>
       </c>
     </row>
     <row r="145" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A145" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B145" t="s">
-        <v>152</v>
+        <v>220</v>
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.2">
@@ -3188,369 +3195,377 @@
         <v>39</v>
       </c>
       <c r="B146" t="s">
-        <v>221</v>
+        <v>152</v>
       </c>
     </row>
     <row r="147" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
-        <v>2</v>
+        <v>39</v>
       </c>
       <c r="B147" t="s">
-        <v>57</v>
-      </c>
-      <c r="D147" t="s">
-        <v>148</v>
-      </c>
-      <c r="E147" t="s">
-        <v>268</v>
-      </c>
-      <c r="G147" t="s">
-        <v>86</v>
-      </c>
-      <c r="L147" t="s">
-        <v>233</v>
+        <v>221</v>
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B148" t="s">
+        <v>57</v>
+      </c>
+      <c r="D148" t="s">
+        <v>148</v>
+      </c>
+      <c r="E148" t="s">
+        <v>268</v>
+      </c>
+      <c r="G148" t="s">
+        <v>86</v>
+      </c>
+      <c r="L148" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B149" t="s">
         <v>58</v>
       </c>
-      <c r="D148" t="s">
+      <c r="D149" t="s">
         <v>153</v>
       </c>
-      <c r="E148" t="s">
+      <c r="E149" t="s">
         <v>269</v>
       </c>
-      <c r="F148" t="s">
+      <c r="F149" t="s">
         <v>87</v>
-      </c>
-      <c r="G148" t="s">
-        <v>8</v>
-      </c>
-      <c r="L148" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B149" t="s">
-        <v>59</v>
       </c>
       <c r="G149" t="s">
         <v>8</v>
       </c>
+      <c r="L149" t="s">
+        <v>232</v>
+      </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A150" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B150" t="s">
-        <v>155</v>
-      </c>
-      <c r="C150" t="s">
-        <v>154</v>
+        <v>59</v>
       </c>
       <c r="G150" t="s">
-        <v>238</v>
+        <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="B151" t="s">
-        <v>60</v>
+        <v>155</v>
+      </c>
+      <c r="C151" t="s">
+        <v>154</v>
+      </c>
+      <c r="G151" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="B152" t="s">
-        <v>62</v>
-      </c>
-      <c r="C152" t="s">
-        <v>149</v>
+        <v>60</v>
       </c>
     </row>
     <row r="153" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A153" s="3" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="B153" t="s">
-        <v>63</v>
+        <v>62</v>
+      </c>
+      <c r="C153" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A154" s="3" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="B154" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="155" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A155" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B155" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A156" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B156" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="157" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A157" s="3" t="s">
-        <v>61</v>
+        <v>0</v>
       </c>
       <c r="B157" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A158" s="3" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="B158" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="159" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A159" s="3" t="s">
-        <v>61</v>
+        <v>8</v>
       </c>
       <c r="B159" t="s">
-        <v>69</v>
-      </c>
-      <c r="G159" t="s">
-        <v>237</v>
+        <v>68</v>
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A160" s="3" t="s">
-        <v>2</v>
+        <v>61</v>
       </c>
       <c r="B160" t="s">
+        <v>69</v>
+      </c>
+      <c r="G160" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A161" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
         <v>70</v>
       </c>
-      <c r="G160" t="s">
+      <c r="G161" t="s">
         <v>239</v>
       </c>
     </row>
-    <row r="161" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A161" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B161" t="s">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B162" t="s">
         <v>222</v>
       </c>
     </row>
-    <row r="162" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A162" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B162" t="s">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A163" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B163" t="s">
         <v>71</v>
       </c>
-      <c r="C162" t="s">
+      <c r="C163" t="s">
         <v>156</v>
       </c>
     </row>
-    <row r="163" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="s">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A164" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B163" t="s">
+      <c r="B164" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="164" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B164" t="s">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A165" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B165" t="s">
         <v>223</v>
       </c>
     </row>
-    <row r="165" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A165" s="3" t="s">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A166" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B165" t="s">
+      <c r="B166" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="166" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A166" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B166" t="s">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A167" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B167" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="167" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A167" s="3" t="s">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B167" t="s">
+      <c r="B168" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="168" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A168" s="3" t="s">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B168" t="s">
+      <c r="B169" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="169" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A169" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B169" t="s">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="170" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="s">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B170" t="s">
+      <c r="B171" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="171" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A171" s="3" t="s">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B171" t="s">
+      <c r="B172" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="172" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" t="s">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B173" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="173" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B173" t="s">
+      <c r="B174" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="174" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B174" t="s">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B175" t="s">
         <v>225</v>
       </c>
     </row>
-    <row r="175" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B175" t="s">
+      <c r="B176" t="s">
         <v>81</v>
-      </c>
-    </row>
-    <row r="176" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B176" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="177" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
-        <v>61</v>
+        <v>2</v>
       </c>
       <c r="B177" t="s">
-        <v>226</v>
+        <v>82</v>
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A178" s="3" t="s">
-        <v>0</v>
+        <v>61</v>
       </c>
       <c r="B178" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B179" t="s">
         <v>240</v>
       </c>
-      <c r="C178" t="s">
+      <c r="C179" t="s">
         <v>157</v>
       </c>
-      <c r="D178" t="s">
+      <c r="D179" t="s">
         <v>153</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B179" t="s">
-        <v>241</v>
-      </c>
-      <c r="G179" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B180" t="s">
-        <v>83</v>
-      </c>
-      <c r="D180" t="s">
-        <v>158</v>
-      </c>
-      <c r="F180" t="s">
-        <v>87</v>
+        <v>241</v>
       </c>
       <c r="G180" t="s">
-        <v>86</v>
+        <v>242</v>
       </c>
     </row>
     <row r="181" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B181" t="s">
-        <v>227</v>
+        <v>83</v>
+      </c>
+      <c r="D181" t="s">
+        <v>158</v>
+      </c>
+      <c r="F181" t="s">
+        <v>87</v>
+      </c>
+      <c r="G181" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B182" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="183" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B183" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B184" t="s">
         <v>229</v>
       </c>
-      <c r="D183" t="s">
+      <c r="D184" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B184" t="s">
+    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B185" t="s">
         <v>230</v>
       </c>
-      <c r="L184" t="s">
+      <c r="L185" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L185" t="s">
+    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L186" t="s">
         <v>84</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{442B30C7-4153-41AF-BD2D-17DAC86E5406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37D0D19-AD36-4177-A537-643CBD479DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="6810" yWindow="3045" windowWidth="16755" windowHeight="13455" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="303">
   <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -87,10 +87,6 @@
   </si>
   <si>
     <t>来我这住，正好凑个伴。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明刻意挤出坏笑。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -176,18 +172,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒隐约觉得不对劲，却没再追问。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明失眠，此刻正看着熟睡的漠寒，思绪翻涌。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>他小时候老是被当成“头脑简单的傻大个”，总被欺负。直到漠寒出现——那是第一个护着他的人。他还记得小学时，大冬天被关在宿舍门外，冻得发抖。漠寒在里面劝不动人，直接一脚踹坏了门。那天室友骂漠寒是“护主的狗”，他第一次发了疯似的打人，连漠寒都拦不住。从那以后，再没人敢欺负他。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>次日清晨，漠寒和叶苏明一同去以钛科学。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -236,10 +220,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>不必，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>刘宇轩敲了敲笔</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -252,10 +232,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>面试其实是测试高压下的反应——不过说实话，以钛科学确实不错。以打工人或科研人员的身份，我能这么说。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>那您怎么会在人事部？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -604,14 +580,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒盯着“录取通知”四个字，指尖悬在最后一行。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明气喘吁吁地跑进来，坐在他旁边，把午饭放一边，用湿漉的皮肤贴着他。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>音效/车子行驶而过</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -620,10 +588,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>等空调凉下来就好了……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>以钛科学</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -664,10 +628,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>不久，一个抱着箱子的青年走进来，里面似乎是文件。他和叶苏明年纪相仿，稍矮些。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>音效/摩擦1|音效/脚步声</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -712,10 +672,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒不安地望向窗外：路面车流如织，空中悬浮车穿梭；高楼如浪涛起伏，被风揉碎的光影里，飞行器盘旋而过。有的楼宇嵌着巨幕，立体投影与平面影像交织，灯红酒绿中透着繁忙。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>手机屏幕仍然亮着，联系人名“叶苏明”正闪烁着未读信息，屏幕上浮现出他曾经的消息：“我就知道你可以”</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -736,14 +692,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒接起电话，声音略显沙哑，试图压抑内心的波动。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明天没工期，出来玩？难得见面一次。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>等我确定被录进以钛科学后再过去，不然……可能得去别的地方找地方住。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -788,10 +736,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>没、没有。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>询问1</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -852,10 +796,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒拿起那张纸，快速扫了一眼，心猛地一沉——是叶苏明的心理诊断单，上面写着“中度抑郁”。他往桌上瞥了瞥，没看到药，便把单子原样塞回键盘下，轻轻挠了挠头，尽力让自己保持冷静。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>（这是？）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -872,10 +812,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>他一边说一边遮遮掩掩地走到电脑前，偷偷把诊断单折起来塞进抽屉——那个抽屉漠寒刚看过，只有几本言情小说。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>其实我挺好奇为什么你喜欢‘0’这个数字。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -888,30 +824,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>刚才队长说，我们队可能要来个从大公司离职的新队员，我不用猜也知道是你！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>不说点什么吗？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>我是怎么被分过来的？</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>前几天队里有人……问这个干嘛？反正有空位，我就想着拉过你过来了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;下午，叶苏明比漠寒还兴奋，带着漠寒逛了不少地方，仿佛自己才是被录用的那个人，兴致勃勃地聊着未来的工作。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;一天结束，两人挤进卧室睡觉。这晚叶苏明还是失眠，此刻他隔着些距离，着熟睡的漠寒，思绪翻涌。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>他总黏着漠寒，几乎形影不离。说不清为何，和漠寒待着时，心里那股隐痛会消散，甚至生出几分贪恋。说喜欢太浅，说不喜欢又太假。而且总有种冲动，想护着漠寒——哪怕多数时候是漠寒在保护他。他瞎想过很多：前世约定？命运安排？</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -948,10 +864,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>那我们FoxTi是元核全装队啊——可惜我不会用，不知道你会不会。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>会议是专门为漠寒开设的，内容简短，讲解了规章制度、未来规划和任务指标，最后以个人名义欢迎了他。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1048,14 +960,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>（我被漠寒帮助过太多次了，我该怎么回报他……？）</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>别老蹭我……你都热得只剩下内裤了（迷糊）……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>漠寒凝视着刘宇轩，没有说话。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1064,10 +968,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>你若拒绝，FoxTi的新人怕是等不到你指导，就死在任务中了。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>头像统一 &gt;&gt; True|解锁档案 &gt;&gt; 虚空|解锁档案 &gt;&gt; 虚空平面|解锁档案 &gt;&gt; 虚空流</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1151,16 +1051,198 @@
     <t>#TAG</t>
   </si>
   <si>
+    <t>指令</t>
+  </si>
+  <si>
+    <t>播放立绘动画 &gt;&gt; A_MovedOver_Hit_B 0 1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虽然过去早已落幕，漠寒仍不禁抬手按在额头轻叹。身旁电视开着，他才想起昨夜没关。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他不安地望向窗外：路面车流如织，空中悬浮车穿梭；高楼如浪涛起伏，被风揉碎的光影里，飞行器盘旋而过。有的楼宇嵌着巨幕，立体投影与平面影像交织，灯红酒绿中透着繁忙。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒的声音略显沙哑，试图压抑内心的波动。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大！明天没工期，出来玩？难得见面一次。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒服了一片安眠药，在床上几番辗转</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>TE. HUD层</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>选项</t>
-  </si>
-  <si>
-    <t>TE. HUD层</t>
-  </si>
-  <si>
-    <t>指令</t>
-  </si>
-  <si>
-    <t>播放立绘动画 &gt;&gt; A_MovedOver_Hit_B 0 1</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>没、没有。本来想接你的。睡过头了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒小声嚷嚷，拿起那张纸，快速扫了一眼，心猛地一沉——是叶苏明的心理诊断单，上面写着“中度抑郁”。他往桌上瞥了瞥，没看到药，便把单子原样塞回键盘下，轻轻挠了挠头。从小学到现在，他眼中的叶苏明好像早就不是那个患得患失、抑郁寡欢的他了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他一边说一边遮遮掩掩地走到电脑前，偷偷把诊断单折起来塞进抽屉——那个抽屉漠寒刚看过，只有几本言情小说，封面签了一个“刘”字。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你最近睡得还好吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>咩？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我说……你最近怎么样？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还不错啊，老大。你呢？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我？嗯……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒看了眼叶苏明，尾巴不禁下垂</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>整理完漠寒的东西，叶苏明提议去附近的健身房，漠寒嘴上说着不想，最后还是决定陪叶苏明一趟。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你不错就好，我还不错。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这时叶苏明气喘吁吁地跑进来，坐在他旁边，把午饭放一边，用湿漉的皮肤贴着他。叶苏明一把搂住漠寒，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大！我刚才队长说，我们队可能要来个从大公司离职的新队员，我不用猜也知道是你！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>为什么能这么巧？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>前几天队里有人……问这个干嘛？反正有空位，我就想着拉你过来了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒隐约觉得不对劲，却没再追问。之后，叶苏明似乎比漠寒还兴奋，带着漠寒逛了不少地方，仿佛自己才是被录用的那个人，兴致勃勃地聊着未来的工作。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;快傍晚，叶苏明突然提议去看一场电影，于是把漠寒领到别人都推荐的电影院。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>可惜的是，他们前往的影院这个时间点仅剩下一部恐怖电影尚未上映。漠寒站在电影院门口望着回家的方向，而叶苏明在恐怖片的海报前踟蹰，内心挣扎。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>回家吧？不早了，而且看了你容易做噩梦。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>我也不是小孩子了，老大！来都来了，不看一趟？反正咱家里现在有两个人。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>噗呲，好，我倒是无所谓。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>叶苏明坚定地走进电影院，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;一天结束，两人回到公寓。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒，能不能在厕所外面等我……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>都说别看恐怖片……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在叶苏明洗澡的间隙，漠寒偷偷把行李箱中没拿出来的安眠药用团纸包着，几番挣扎，还是选择丢进垃圾桶，然后继续守在门口刷视频。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>待漠寒洗完澡，出来后发现叶苏明也在门口守着，不禁一笑。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>两人挤进卧室睡觉。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这晚叶苏明失眠——或是日常失眠，或是真的被恐怖片吓到了。此刻他隔着些距离，看着“熟睡”的漠寒，思绪翻涌。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>后来，叶苏明找到漠寒问为什么帮他，漠寒的回答让他记了一辈子。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他小时候老是被当成“头脑简单的傻大个”，总被欺负。漠寒是第一个护着他的人。他还记得，一次冬天被关在宿舍门外，冻得发抖。漠寒在里面劝不动人，直接一脚踹坏了门。那天室友骂漠寒是“护主的狗”，叶苏明第一次发了疯似的打人，连漠寒都拦不住。从那以后，再没人敢欺负他。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他回想起第一次和漠寒相遇的那一天，他被一头熊人，一头龙人联合困在厕所的隔间里。他倒在地上，恐惧地用眼神乞求门口的魔鬼。门外的两人嬉笑，一人操着扫把，一人死死把叶苏明往地上按。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这不是第一次，而班上的人也习以为常。一天，漠寒恰好路过，龙人举着扫把说别管闲事，不知怎么，漠寒就和两名霸凌的人打了一架，被记了过。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>想着，叶苏明往漠寒那挪了挪。漠寒重重吸了口气，让叶苏明惊了一下。看漠寒舔了舔嘴唇，叶苏明才安下心来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（我被老大帮助过太多次了，我该怎么回报他……？）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒，</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FoxTi目前缺一个有经验的成员，我不希望再看到有人因为经验不足出事。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>面试其实是测试高压下的反应——不过说实话，以钛科学确实不错。以‘打工人’或科研人员的身份，我能这么说。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不久，一个抱着箱子的青年走进来，里面似乎是文件。他是 FoxTi队长云叶枫。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>那我们FoxTi是元核全装队啊——可惜我不会用，不知道你会不会。可惜……不像叶苏明，我不使用特殊装备我的元核几乎走不上道——不知道你会不会用元核。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1606,7 +1688,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF46EA-649E-46D2-A2F1-55ADFE170F2E}">
-  <dimension ref="A1:L186"/>
+  <dimension ref="A1:L205"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -1619,40 +1701,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
-        <v>270</v>
+        <v>245</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>271</v>
+        <v>246</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>272</v>
+        <v>247</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>273</v>
+        <v>248</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>274</v>
+        <v>249</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>275</v>
+        <v>250</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>276</v>
+        <v>251</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>277</v>
+        <v>252</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>278</v>
+        <v>253</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>279</v>
+        <v>262</v>
       </c>
       <c r="K1" s="5" t="s">
-        <v>280</v>
+        <v>261</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>281</v>
+        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1660,41 +1742,41 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="F2" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="L2" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="F3" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F4" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.2">
@@ -1702,11 +1784,11 @@
         <v>0</v>
       </c>
       <c r="B5" t="s">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="C5" s="6"/>
       <c r="D5" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E5" s="6"/>
       <c r="F5" s="6"/>
@@ -1715,15 +1797,15 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="C6" s="6"/>
       <c r="D6" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="E6" s="6"/>
       <c r="F6" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G6" s="6"/>
       <c r="H6" s="6"/>
@@ -1733,7 +1815,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1741,17 +1823,17 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1759,10 +1841,10 @@
         <v>0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="D11" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.2">
@@ -1770,16 +1852,16 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="D12" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>244</v>
+        <v>222</v>
       </c>
       <c r="F12" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.2">
@@ -1787,19 +1869,19 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>243</v>
+        <v>221</v>
       </c>
       <c r="F13" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="H13" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.2">
@@ -1807,41 +1889,29 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="D14" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="F14" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D15" t="s">
-        <v>96</v>
+        <v>256</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C16" t="s">
-        <v>98</v>
+        <v>257</v>
       </c>
       <c r="D16" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1849,30 +1919,33 @@
         <v>3</v>
       </c>
       <c r="B17" t="s">
-        <v>254</v>
+        <v>93</v>
       </c>
       <c r="C17" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D17" t="s">
-        <v>97</v>
-      </c>
-      <c r="L17" t="s">
-        <v>261</v>
+        <v>91</v>
+      </c>
+      <c r="F17" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>168</v>
+        <v>230</v>
+      </c>
+      <c r="C18" t="s">
+        <v>94</v>
       </c>
       <c r="D18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F18" t="s">
-        <v>92</v>
+        <v>91</v>
+      </c>
+      <c r="L18" t="s">
+        <v>236</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -1880,61 +1953,55 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="D19" t="s">
-        <v>101</v>
+        <v>95</v>
+      </c>
+      <c r="F19" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>258</v>
+        <v>158</v>
       </c>
       <c r="D20" t="s">
         <v>95</v>
       </c>
-      <c r="F20" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>170</v>
-      </c>
-      <c r="C21" t="s">
-        <v>102</v>
+        <v>233</v>
       </c>
       <c r="D21" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F21" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>259</v>
+        <v>159</v>
       </c>
       <c r="C22" t="s">
-        <v>103</v>
+        <v>96</v>
       </c>
       <c r="D22" t="s">
-        <v>245</v>
+        <v>82</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
-      </c>
-      <c r="L22" t="s">
-        <v>260</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.2">
@@ -1942,32 +2009,44 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>4</v>
+        <v>234</v>
       </c>
       <c r="C23" t="s">
-        <v>104</v>
+        <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>96</v>
+        <v>223</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>81</v>
+      </c>
+      <c r="L23" t="s">
+        <v>235</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B24" t="s">
-        <v>5</v>
+        <v>4</v>
+      </c>
+      <c r="C24" t="s">
+        <v>98</v>
+      </c>
+      <c r="D24" t="s">
+        <v>90</v>
+      </c>
+      <c r="F24" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.2">
@@ -1975,57 +2054,57 @@
         <v>3</v>
       </c>
       <c r="B26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26" t="s">
-        <v>107</v>
+        <v>6</v>
       </c>
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>106</v>
+        <v>3</v>
       </c>
       <c r="B27" t="s">
-        <v>257</v>
-      </c>
-      <c r="G27" t="s">
-        <v>86</v>
-      </c>
-      <c r="L27" t="s">
-        <v>256</v>
+        <v>99</v>
+      </c>
+      <c r="C27" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>171</v>
-      </c>
-      <c r="C28" t="s">
-        <v>109</v>
+        <v>232</v>
       </c>
       <c r="G28" t="s">
+        <v>80</v>
+      </c>
+      <c r="L28" t="s">
         <v>231</v>
-      </c>
-      <c r="L28" t="s">
-        <v>232</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>172</v>
+        <v>160</v>
+      </c>
+      <c r="C29" t="s">
+        <v>103</v>
+      </c>
+      <c r="G29" t="s">
+        <v>209</v>
+      </c>
+      <c r="L29" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A30" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -2033,55 +2112,55 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>7</v>
+        <v>258</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A32" s="3" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>174</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="B33" t="s">
-        <v>9</v>
+        <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>2</v>
+        <v>104</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="B36" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="B37" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.2">
@@ -2089,44 +2168,44 @@
         <v>2</v>
       </c>
       <c r="B38" t="s">
-        <v>6</v>
+        <v>162</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="3" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="B40" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="3" t="s">
-        <v>110</v>
+        <v>2</v>
       </c>
       <c r="B41" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B42" t="s">
-        <v>178</v>
+        <v>13</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>0</v>
+        <v>104</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
@@ -2134,74 +2213,71 @@
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>166</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A45" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B45" t="s">
-        <v>179</v>
+        <v>105</v>
+      </c>
+      <c r="D45" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" t="s">
+        <v>221</v>
+      </c>
+      <c r="G45" t="s">
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
-        <v>111</v>
-      </c>
-      <c r="D46" t="s">
-        <v>96</v>
-      </c>
-      <c r="E46" t="s">
-        <v>243</v>
-      </c>
-      <c r="G46" t="s">
-        <v>247</v>
+        <v>106</v>
+      </c>
+      <c r="C46" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>112</v>
-      </c>
-      <c r="C47" t="s">
-        <v>109</v>
+        <v>260</v>
       </c>
       <c r="D47" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F47" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G47" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B48" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="E48" t="s">
-        <v>246</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>114</v>
+        <v>108</v>
       </c>
       <c r="C49" t="s">
-        <v>117</v>
+        <v>111</v>
       </c>
       <c r="D49" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="E49" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
@@ -2209,13 +2285,13 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>248</v>
+        <v>226</v>
       </c>
       <c r="D50" t="s">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="G50" t="s">
-        <v>86</v>
+        <v>80</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
@@ -2223,19 +2299,19 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>116</v>
+        <v>110</v>
       </c>
       <c r="D51" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="E51" t="s">
-        <v>262</v>
+        <v>237</v>
       </c>
       <c r="F51" t="s">
-        <v>87</v>
+        <v>81</v>
       </c>
       <c r="G51" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -2243,255 +2319,260 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
+        <v>112</v>
+      </c>
+      <c r="I52" t="s">
         <v>118</v>
       </c>
-      <c r="I52" t="s">
-        <v>124</v>
-      </c>
       <c r="J52" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="L52" t="s">
-        <v>128</v>
+        <v>122</v>
+      </c>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>115</v>
+      </c>
+      <c r="E53" t="s">
+        <v>238</v>
+      </c>
+      <c r="I53" t="s">
+        <v>116</v>
+      </c>
+      <c r="L53" t="s">
+        <v>167</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
+        <v>113</v>
+      </c>
+      <c r="C54" t="s">
+        <v>111</v>
+      </c>
+      <c r="I54" t="s">
+        <v>114</v>
+      </c>
+      <c r="L54" t="s">
         <v>121</v>
       </c>
-      <c r="E54" t="s">
-        <v>263</v>
-      </c>
-      <c r="I54" t="s">
-        <v>122</v>
-      </c>
-      <c r="L54" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="55" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B55" t="s">
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B56" t="s">
+        <v>181</v>
+      </c>
+      <c r="E56" t="s">
+        <v>237</v>
+      </c>
+      <c r="I56" t="s">
         <v>119</v>
       </c>
-      <c r="C55" t="s">
-        <v>117</v>
-      </c>
-      <c r="I55" t="s">
+      <c r="L56" t="s">
         <v>120</v>
-      </c>
-      <c r="L55" t="s">
-        <v>127</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
-        <v>195</v>
-      </c>
-      <c r="E57" t="s">
-        <v>262</v>
-      </c>
-      <c r="I57" t="s">
-        <v>125</v>
-      </c>
-      <c r="L57" t="s">
-        <v>126</v>
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>96</v>
+      </c>
+      <c r="G57" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>16</v>
-      </c>
-      <c r="C58" t="s">
-        <v>102</v>
+        <v>212</v>
       </c>
       <c r="G58" t="s">
-        <v>108</v>
+        <v>213</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A59" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B59" t="s">
-        <v>234</v>
-      </c>
-      <c r="G59" t="s">
-        <v>235</v>
+        <v>169</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>182</v>
+        <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B62" t="s">
-        <v>183</v>
+        <v>85</v>
+      </c>
+      <c r="L62" t="s">
+        <v>255</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>183</v>
-      </c>
-      <c r="L63" t="s">
-        <v>282</v>
+        <v>171</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>184</v>
+        <v>172</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A65" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>185</v>
+        <v>263</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A66" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B66" t="s">
-        <v>186</v>
+        <v>6</v>
+      </c>
+      <c r="D66" t="s">
+        <v>109</v>
+      </c>
+      <c r="I66" t="s">
+        <v>179</v>
+      </c>
+      <c r="J66" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A67" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>6</v>
-      </c>
-      <c r="D67" t="s">
-        <v>115</v>
+        <v>176</v>
       </c>
       <c r="I67" t="s">
-        <v>193</v>
-      </c>
-      <c r="J67" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A68" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>190</v>
-      </c>
-      <c r="I68" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A69" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>191</v>
+        <v>178</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A70" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B70" t="s">
-        <v>192</v>
+        <v>16</v>
+      </c>
+      <c r="C70" t="s">
+        <v>96</v>
+      </c>
+      <c r="D70" t="s">
+        <v>123</v>
+      </c>
+      <c r="F70" t="s">
+        <v>81</v>
+      </c>
+      <c r="I70" t="s">
+        <v>174</v>
+      </c>
+      <c r="L70" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A71" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B71" t="s">
-        <v>17</v>
-      </c>
-      <c r="C71" t="s">
-        <v>102</v>
-      </c>
-      <c r="D71" t="s">
-        <v>129</v>
-      </c>
-      <c r="F71" t="s">
-        <v>87</v>
-      </c>
-      <c r="I71" t="s">
-        <v>188</v>
-      </c>
-      <c r="L71" t="s">
-        <v>194</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A72" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B72" t="s">
-        <v>196</v>
+        <v>183</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A73" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>197</v>
+        <v>184</v>
+      </c>
+      <c r="G73" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A74" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>198</v>
+        <v>185</v>
+      </c>
+      <c r="D74" t="s">
+        <v>123</v>
       </c>
       <c r="G74" t="s">
-        <v>264</v>
+        <v>240</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A75" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B75" t="s">
-        <v>199</v>
+        <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>129</v>
+        <v>126</v>
+      </c>
+      <c r="F75" t="s">
+        <v>81</v>
       </c>
       <c r="G75" t="s">
-        <v>265</v>
+        <v>2</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A76" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="D76" t="s">
-        <v>132</v>
-      </c>
-      <c r="F76" t="s">
-        <v>87</v>
-      </c>
-      <c r="G76" t="s">
-        <v>2</v>
+        <v>0</v>
+      </c>
+      <c r="B76" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -2499,29 +2580,38 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>200</v>
+        <v>187</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A78" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>201</v>
+        <v>188</v>
+      </c>
+      <c r="C78" t="s">
+        <v>127</v>
+      </c>
+      <c r="L78" t="s">
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A79" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>203</v>
-      </c>
-      <c r="C79" t="s">
-        <v>133</v>
+        <v>264</v>
+      </c>
+      <c r="D79" t="s">
+        <v>126</v>
+      </c>
+      <c r="G79" t="s">
+        <v>2</v>
       </c>
       <c r="L79" t="s">
-        <v>266</v>
+        <v>242</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -2529,44 +2619,35 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>202</v>
+        <v>189</v>
+      </c>
+      <c r="C80" t="s">
+        <v>129</v>
       </c>
       <c r="D80" t="s">
-        <v>132</v>
+        <v>128</v>
+      </c>
+      <c r="F80" t="s">
+        <v>86</v>
       </c>
       <c r="G80" t="s">
-        <v>2</v>
+        <v>214</v>
       </c>
       <c r="L80" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A81" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B81" t="s">
-        <v>204</v>
-      </c>
-      <c r="C81" t="s">
-        <v>135</v>
-      </c>
-      <c r="D81" t="s">
-        <v>134</v>
-      </c>
-      <c r="F81" t="s">
-        <v>92</v>
-      </c>
-      <c r="G81" t="s">
-        <v>236</v>
-      </c>
-      <c r="L81" t="s">
-        <v>266</v>
+        <v>17</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A82" s="3" t="s">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B82" t="s">
         <v>18</v>
@@ -2574,73 +2655,73 @@
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B83" t="s">
         <v>20</v>
-      </c>
-      <c r="B83" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A84" s="3" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>21</v>
+        <v>190</v>
+      </c>
+      <c r="D84" t="s">
+        <v>128</v>
+      </c>
+      <c r="F84" t="s">
+        <v>86</v>
+      </c>
+      <c r="G84" t="s">
+        <v>214</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A85" s="3" t="s">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>205</v>
+        <v>191</v>
       </c>
       <c r="D85" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="F85" t="s">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="G85" t="s">
-        <v>236</v>
+        <v>213</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A86" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B86" t="s">
-        <v>206</v>
-      </c>
-      <c r="D86" t="s">
-        <v>132</v>
-      </c>
-      <c r="F86" t="s">
-        <v>92</v>
-      </c>
-      <c r="G86" t="s">
-        <v>235</v>
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A87" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>23</v>
+        <v>265</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A88" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B88" t="s">
-        <v>207</v>
+        <v>23</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A89" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B89" t="s">
         <v>24</v>
@@ -2648,96 +2729,75 @@
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A90" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>25</v>
+        <v>192</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A91" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A92" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>209</v>
+        <v>194</v>
+      </c>
+      <c r="D92" t="s">
+        <v>126</v>
+      </c>
+      <c r="G92" t="s">
+        <v>213</v>
+      </c>
+      <c r="L92" t="s">
+        <v>210</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A93" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>210</v>
-      </c>
-      <c r="D93" t="s">
-        <v>132</v>
-      </c>
-      <c r="G93" t="s">
-        <v>235</v>
-      </c>
-      <c r="L93" t="s">
-        <v>232</v>
+        <v>266</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A94" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B94" t="s">
-        <v>136</v>
-      </c>
-      <c r="D94" t="s">
-        <v>88</v>
-      </c>
-      <c r="F94" t="s">
-        <v>87</v>
-      </c>
-      <c r="G94" t="s">
-        <v>86</v>
-      </c>
-      <c r="L94" t="s">
-        <v>233</v>
+        <v>267</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A95" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B95" t="s">
-        <v>137</v>
-      </c>
-      <c r="D95" t="s">
-        <v>138</v>
-      </c>
-      <c r="F95" t="s">
-        <v>92</v>
+        <v>268</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A96" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>26</v>
-      </c>
-      <c r="C96" t="s">
-        <v>109</v>
-      </c>
-      <c r="L96" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="97" spans="1:12" ht="171" x14ac:dyDescent="0.2">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A97" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B97" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="L97" t="s">
-        <v>130</v>
+        <v>2</v>
+      </c>
+      <c r="B97" t="s">
+        <v>270</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
@@ -2745,18 +2805,15 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>140</v>
-      </c>
-      <c r="L98" t="s">
-        <v>131</v>
+        <v>271</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A99" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C99" t="s">
-        <v>139</v>
+        <v>2</v>
+      </c>
+      <c r="B99" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
@@ -2764,119 +2821,116 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>141</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A101" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="B101" t="s">
+        <v>130</v>
+      </c>
+      <c r="D101" t="s">
+        <v>82</v>
+      </c>
+      <c r="F101" t="s">
+        <v>81</v>
+      </c>
+      <c r="G101" t="s">
+        <v>80</v>
+      </c>
+      <c r="L101" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A102" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B102" t="s">
-        <v>29</v>
+        <v>131</v>
+      </c>
+      <c r="D102" t="s">
+        <v>132</v>
+      </c>
+      <c r="F102" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="103" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A103" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B103" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="104" spans="1:12" x14ac:dyDescent="0.2">
+        <v>25</v>
+      </c>
+      <c r="C103" t="s">
+        <v>103</v>
+      </c>
+      <c r="L103" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" ht="171" x14ac:dyDescent="0.2">
       <c r="A104" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B104" t="s">
-        <v>213</v>
+        <v>26</v>
+      </c>
+      <c r="B104" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="L104" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A105" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B105" t="s">
-        <v>214</v>
+        <v>85</v>
+      </c>
+      <c r="C105" t="s">
+        <v>133</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A106" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>31</v>
+        <v>274</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A107" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>30</v>
+        <v>275</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A108" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B108" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
     </row>
     <row r="109" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A109" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>33</v>
-      </c>
-      <c r="D109" t="s">
-        <v>138</v>
+        <v>195</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A110" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B110" t="s">
-        <v>215</v>
-      </c>
-      <c r="D110" t="s">
-        <v>88</v>
-      </c>
-      <c r="E110" t="s">
-        <v>262</v>
-      </c>
-      <c r="F110" t="s">
-        <v>87</v>
+        <v>276</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A111" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>216</v>
-      </c>
-      <c r="C111" t="s">
-        <v>142</v>
-      </c>
-      <c r="D111" t="s">
-        <v>88</v>
-      </c>
-      <c r="E111" t="s">
-        <v>246</v>
-      </c>
-      <c r="F111" t="s">
-        <v>87</v>
-      </c>
-      <c r="L111" t="s">
-        <v>249</v>
+        <v>277</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
@@ -2884,689 +2938,844 @@
         <v>2</v>
       </c>
       <c r="B112" t="s">
-        <v>252</v>
-      </c>
-      <c r="D112" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="113" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A113" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="114" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A114" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B113" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="114" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A114" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B114" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="115" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A115" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B115" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A116" s="3" t="s">
-        <v>0</v>
-      </c>
+        <v>278</v>
+      </c>
+      <c r="D115" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" x14ac:dyDescent="0.2">
+        <v>279</v>
+      </c>
+      <c r="D116" t="s">
+        <v>82</v>
+      </c>
+      <c r="E116" t="s">
+        <v>237</v>
+      </c>
+      <c r="F116" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B117" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="118" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A118" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B118" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="119" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A119" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B117" t="s">
-        <v>251</v>
-      </c>
-      <c r="D117" t="s">
-        <v>143</v>
-      </c>
-      <c r="E117" t="s">
-        <v>246</v>
-      </c>
-    </row>
-    <row r="118" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A118" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B118" t="s">
-        <v>36</v>
-      </c>
-      <c r="D118" t="s">
-        <v>145</v>
-      </c>
-      <c r="E118" t="s">
-        <v>268</v>
-      </c>
-      <c r="F118" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="119" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A119" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B119" t="s">
-        <v>147</v>
-      </c>
-      <c r="D119" t="s">
-        <v>146</v>
-      </c>
-      <c r="F119" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="120" spans="1:6" x14ac:dyDescent="0.2">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="120" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A120" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="C120" t="s">
-        <v>102</v>
-      </c>
-      <c r="D120" t="s">
-        <v>148</v>
-      </c>
-      <c r="F120" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="121" spans="1:6" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+      <c r="B120" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="122" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A122" s="3" t="s">
-        <v>39</v>
-      </c>
+        <v>284</v>
+      </c>
+    </row>
+    <row r="122" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B122" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="123" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="124" spans="1:6" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+      <c r="C123" t="s">
+        <v>134</v>
+      </c>
+      <c r="D123" t="s">
+        <v>82</v>
+      </c>
+      <c r="E123" t="s">
+        <v>224</v>
+      </c>
+      <c r="F123" t="s">
+        <v>81</v>
+      </c>
+      <c r="L123" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>39</v>
+        <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="125" spans="1:6" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="126" spans="1:6" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="127" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A127" s="3" t="s">
-        <v>2</v>
-      </c>
+        <v>288</v>
+      </c>
+    </row>
+    <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="128" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A128" s="3" t="s">
-        <v>0</v>
-      </c>
+        <v>289</v>
+      </c>
+    </row>
+    <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>43</v>
-      </c>
-      <c r="C128" t="s">
-        <v>149</v>
+        <v>290</v>
+      </c>
+      <c r="D128" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>44</v>
+        <v>291</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A130" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B130" t="s">
-        <v>45</v>
+        <v>294</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A131" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="B131" t="s">
-        <v>46</v>
+        <v>295</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A132" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B132" t="s">
-        <v>47</v>
+        <v>292</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A133" s="3" t="s">
-        <v>39</v>
-      </c>
       <c r="B133" t="s">
-        <v>48</v>
+        <v>293</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A134" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B134" t="s">
-        <v>49</v>
-      </c>
-      <c r="C134" t="s">
-        <v>150</v>
+        <v>296</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>255</v>
+        <v>196</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>50</v>
+        <v>297</v>
+      </c>
+      <c r="D136" t="s">
+        <v>135</v>
+      </c>
+      <c r="E136" t="s">
+        <v>224</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A137" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B137" t="s">
-        <v>51</v>
+        <v>32</v>
+      </c>
+      <c r="D137" t="s">
+        <v>136</v>
+      </c>
+      <c r="E137" t="s">
+        <v>243</v>
+      </c>
+      <c r="F137" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>39</v>
+        <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>250</v>
+        <v>138</v>
+      </c>
+      <c r="D138" t="s">
+        <v>137</v>
+      </c>
+      <c r="F138" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B139" t="s">
-        <v>253</v>
+        <v>85</v>
+      </c>
+      <c r="C139" t="s">
+        <v>96</v>
+      </c>
+      <c r="D139" t="s">
+        <v>139</v>
+      </c>
+      <c r="F139" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A140" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B140" t="s">
-        <v>55</v>
-      </c>
-      <c r="C140" t="s">
-        <v>151</v>
-      </c>
-      <c r="F140" t="s">
-        <v>87</v>
+        <v>33</v>
       </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A141" s="3" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="B141" t="s">
-        <v>52</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A142" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>53</v>
+        <v>198</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A143" s="3" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B143" t="s">
-        <v>56</v>
+        <v>36</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A144" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B144" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B145" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B146" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B147" t="s">
         <v>39</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C147" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B148" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B149" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B150" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B151" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B152" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B153" t="s">
+        <v>44</v>
+      </c>
+      <c r="C153" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B154" t="s">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B155" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B156" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B157" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A159" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B159" t="s">
+        <v>49</v>
+      </c>
+      <c r="C159" t="s">
+        <v>142</v>
+      </c>
+      <c r="F159" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A160" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B160" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A161" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B161" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B162" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A163" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B163" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A164" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B164" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A165" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B165" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A166" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B166" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A167" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B167" t="s">
+        <v>51</v>
+      </c>
+      <c r="D167" t="s">
+        <v>139</v>
+      </c>
+      <c r="E167" t="s">
+        <v>243</v>
+      </c>
+      <c r="G167" t="s">
+        <v>80</v>
+      </c>
+      <c r="L167" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" t="s">
+        <v>52</v>
+      </c>
+      <c r="D168" t="s">
+        <v>144</v>
+      </c>
+      <c r="E168" t="s">
+        <v>244</v>
+      </c>
+      <c r="F168" t="s">
+        <v>81</v>
+      </c>
+      <c r="G168" t="s">
+        <v>8</v>
+      </c>
+      <c r="L168" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B169" t="s">
+        <v>53</v>
+      </c>
+      <c r="G169" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s">
+        <v>301</v>
+      </c>
+      <c r="C170" t="s">
+        <v>145</v>
+      </c>
+      <c r="G170" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B171" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B145" t="s">
+    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" t="s">
+        <v>56</v>
+      </c>
+      <c r="C172" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B173" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B174" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B175" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B176" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B177" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B178" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B179" t="s">
+        <v>63</v>
+      </c>
+      <c r="G179" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B180" t="s">
+        <v>64</v>
+      </c>
+      <c r="G180" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B181" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A182" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B182" t="s">
+        <v>65</v>
+      </c>
+      <c r="C182" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B183" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B184" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B185" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A186" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B186" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B187" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A188" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B188" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B189" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B190" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B191" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A192" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B192" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="193" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A193" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B193" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="194" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A194" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B194" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="195" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A195" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B195" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="196" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A196" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B196" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="197" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A197" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B197" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="198" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A198" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B198" t="s">
+        <v>218</v>
+      </c>
+      <c r="C198" t="s">
+        <v>147</v>
+      </c>
+      <c r="D198" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B199" t="s">
+        <v>219</v>
+      </c>
+      <c r="G199" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B146" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B147" t="s">
-        <v>221</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B148" t="s">
-        <v>57</v>
-      </c>
-      <c r="D148" t="s">
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B200" t="s">
+        <v>77</v>
+      </c>
+      <c r="D200" t="s">
         <v>148</v>
       </c>
-      <c r="E148" t="s">
-        <v>268</v>
-      </c>
-      <c r="G148" t="s">
-        <v>86</v>
-      </c>
-      <c r="L148" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A149" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B149" t="s">
-        <v>58</v>
-      </c>
-      <c r="D149" t="s">
-        <v>153</v>
-      </c>
-      <c r="E149" t="s">
-        <v>269</v>
-      </c>
-      <c r="F149" t="s">
-        <v>87</v>
-      </c>
-      <c r="G149" t="s">
-        <v>8</v>
-      </c>
-      <c r="L149" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B150" t="s">
-        <v>59</v>
-      </c>
-      <c r="G150" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A151" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B151" t="s">
-        <v>155</v>
-      </c>
-      <c r="C151" t="s">
-        <v>154</v>
-      </c>
-      <c r="G151" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B152" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B153" t="s">
-        <v>62</v>
-      </c>
-      <c r="C153" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B154" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B155" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B156" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B157" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B158" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B159" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B160" t="s">
-        <v>69</v>
-      </c>
-      <c r="G160" t="s">
-        <v>237</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A161" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B161" t="s">
-        <v>70</v>
-      </c>
-      <c r="G161" t="s">
-        <v>239</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A162" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B162" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B163" t="s">
-        <v>71</v>
-      </c>
-      <c r="C163" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B164" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A165" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B165" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A166" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B166" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A167" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B167" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A168" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B168" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A169" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B169" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B170" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A171" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B171" t="s">
+      <c r="F200" t="s">
+        <v>81</v>
+      </c>
+      <c r="G200" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B201" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B202" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B203" t="s">
+        <v>207</v>
+      </c>
+      <c r="D203" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="204" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A204" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B204" t="s">
+        <v>208</v>
+      </c>
+      <c r="L204" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L205" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B172" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B173" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B174" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B175" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B176" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="177" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B177" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="178" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B178" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="179" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B179" t="s">
-        <v>240</v>
-      </c>
-      <c r="C179" t="s">
-        <v>157</v>
-      </c>
-      <c r="D179" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="180" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B180" t="s">
-        <v>241</v>
-      </c>
-      <c r="G180" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="181" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B181" t="s">
-        <v>83</v>
-      </c>
-      <c r="D181" t="s">
-        <v>158</v>
-      </c>
-      <c r="F181" t="s">
-        <v>87</v>
-      </c>
-      <c r="G181" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="182" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B182" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="183" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B183" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="184" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B184" t="s">
-        <v>229</v>
-      </c>
-      <c r="D184" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="185" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B185" t="s">
-        <v>230</v>
-      </c>
-      <c r="L185" t="s">
-        <v>233</v>
-      </c>
-    </row>
-    <row r="186" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L186" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37D0D19-AD36-4177-A537-643CBD479DBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CD4C6F-7892-4C23-B125-DF3361DB237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6810" yWindow="3045" windowWidth="16755" windowHeight="13455" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="303">
   <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -452,10 +452,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒 &gt;&gt; 淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>音效/手机消息</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -880,10 +876,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒_上裸 &gt;&gt; 淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>头像统一 &gt;&gt; False</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -896,14 +888,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒|叶苏明_上裸 &gt;&gt; 淡入</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>叶苏明_上裸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>叶苏明|云叶枫</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -944,10 +928,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒_上裸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;淡入&gt;&lt;中心文本&gt;金灿的晨光抚上脸颊时，蝉鸣与鸟语已交织成网。简单洗漱、收拾行李，退房后他按叶苏明给的路线乘车，再次路过以钛科学大楼——原来叶苏明的住处离这很近。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1000,14 +980,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒|叶苏明_上裸</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>漠寒|叶苏明_上裸 &gt;&gt; 淡出</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>继续背景音乐 &gt;&gt; Airport Lounge</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1243,6 +1215,30 @@
   </si>
   <si>
     <t>那我们FoxTi是元核全装队啊——可惜我不会用，不知道你会不会。可惜……不像叶苏明，我不使用特殊装备我的元核几乎走不上道——不知道你会不会用元核。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒_裸 &gt;&gt; 淡入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒 &gt;&gt; 淡入</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒|叶苏明_裸 &gt;&gt; 淡入</t>
+  </si>
+  <si>
+    <t>^漠寒|叶苏明_裸</t>
+  </si>
+  <si>
+    <t>^漠寒|叶苏明_裸 &gt;&gt; 淡出</t>
+  </si>
+  <si>
+    <t>叶苏明_裸</t>
+  </si>
+  <si>
+    <t>背景明度 &gt;&gt; 1.0</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1701,40 +1697,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="H1" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>246</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="J1" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>247</v>
-      </c>
-      <c r="D1" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="E1" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="G1" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="H1" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>253</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>261</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>254</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1748,7 +1744,7 @@
         <v>82</v>
       </c>
       <c r="E2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F2" t="s">
         <v>81</v>
@@ -1815,7 +1811,7 @@
         <v>1</v>
       </c>
       <c r="B7" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.2">
@@ -1823,17 +1819,17 @@
         <v>0</v>
       </c>
       <c r="B8" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B9" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.2">
@@ -1841,7 +1837,7 @@
         <v>0</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D11" t="s">
         <v>88</v>
@@ -1852,13 +1848,13 @@
         <v>2</v>
       </c>
       <c r="B12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D12" t="s">
         <v>82</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F12" t="s">
         <v>86</v>
@@ -1869,13 +1865,13 @@
         <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
         <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="F13" t="s">
         <v>86</v>
@@ -1889,7 +1885,7 @@
         <v>0</v>
       </c>
       <c r="B14" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D14" t="s">
         <v>90</v>
@@ -1897,10 +1893,16 @@
       <c r="F14" t="s">
         <v>86</v>
       </c>
+      <c r="G14" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>256</v>
+        <v>249</v>
+      </c>
+      <c r="G15" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1908,10 +1910,13 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
         <v>90</v>
+      </c>
+      <c r="G16" t="s">
+        <v>296</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1930,13 +1935,16 @@
       <c r="F17" t="s">
         <v>81</v>
       </c>
+      <c r="G17" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
@@ -1945,7 +1953,7 @@
         <v>91</v>
       </c>
       <c r="L18" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -1953,7 +1961,7 @@
         <v>0</v>
       </c>
       <c r="B19" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D19" t="s">
         <v>95</v>
@@ -1967,7 +1975,7 @@
         <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D20" t="s">
         <v>95</v>
@@ -1978,7 +1986,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
         <v>89</v>
@@ -1992,7 +2000,7 @@
         <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C22" t="s">
         <v>96</v>
@@ -2009,19 +2017,19 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="C23" t="s">
         <v>97</v>
       </c>
       <c r="D23" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="F23" t="s">
         <v>81</v>
       </c>
       <c r="L23" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -2073,13 +2081,10 @@
         <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>232</v>
-      </c>
-      <c r="G28" t="s">
-        <v>80</v>
+        <v>227</v>
       </c>
       <c r="L28" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -2087,16 +2092,13 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C29" t="s">
-        <v>103</v>
-      </c>
-      <c r="G29" t="s">
-        <v>209</v>
+        <v>102</v>
       </c>
       <c r="L29" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.2">
@@ -2104,7 +2106,7 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="31" spans="1:12" x14ac:dyDescent="0.2">
@@ -2112,7 +2114,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -2123,15 +2125,15 @@
         <v>7</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A33" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A34" s="3" t="s">
         <v>2</v>
       </c>
@@ -2139,15 +2141,15 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A35" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B35" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A36" s="3" t="s">
         <v>2</v>
       </c>
@@ -2155,47 +2157,47 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A37" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B37" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A38" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B38" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B39" t="s">
         <v>162</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A39" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B39" t="s">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A40" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" t="s">
         <v>163</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A40" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B40" t="s">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A41" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
         <v>164</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A41" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B41" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A42" s="3" t="s">
         <v>0</v>
       </c>
@@ -2203,78 +2205,72 @@
         <v>13</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A43" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B43" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A44" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D45" t="s">
         <v>90</v>
       </c>
       <c r="E45" t="s">
-        <v>221</v>
-      </c>
-      <c r="G45" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B46" t="s">
+        <v>105</v>
+      </c>
+      <c r="C46" t="s">
+        <v>102</v>
+      </c>
+      <c r="D46" t="s">
+        <v>82</v>
+      </c>
+      <c r="F46" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B47" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B48" t="s">
         <v>106</v>
       </c>
-      <c r="C46" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B47" t="s">
-        <v>260</v>
-      </c>
-      <c r="D47" t="s">
-        <v>82</v>
-      </c>
-      <c r="F47" t="s">
-        <v>81</v>
-      </c>
-      <c r="G47" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B48" t="s">
-        <v>107</v>
-      </c>
       <c r="E48" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D49" t="s">
         <v>82</v>
       </c>
       <c r="E49" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F49" t="s">
         <v>81</v>
@@ -2285,7 +2281,7 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="D50" t="s">
         <v>82</v>
@@ -2299,19 +2295,19 @@
         <v>2</v>
       </c>
       <c r="B51" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D51" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F51" t="s">
         <v>81</v>
       </c>
       <c r="G51" t="s">
-        <v>102</v>
+        <v>297</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -2319,58 +2315,58 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="I52" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J52" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L52" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
+        <v>114</v>
+      </c>
+      <c r="E53" t="s">
+        <v>233</v>
+      </c>
+      <c r="I53" t="s">
         <v>115</v>
       </c>
-      <c r="E53" t="s">
-        <v>238</v>
-      </c>
-      <c r="I53" t="s">
-        <v>116</v>
-      </c>
       <c r="L53" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B54" t="s">
+        <v>112</v>
+      </c>
+      <c r="C54" t="s">
+        <v>110</v>
+      </c>
+      <c r="I54" t="s">
         <v>113</v>
       </c>
-      <c r="C54" t="s">
-        <v>111</v>
-      </c>
-      <c r="I54" t="s">
-        <v>114</v>
-      </c>
       <c r="L54" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B56" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="E56" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="I56" t="s">
+        <v>118</v>
+      </c>
+      <c r="L56" t="s">
         <v>119</v>
-      </c>
-      <c r="L56" t="s">
-        <v>120</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
@@ -2381,15 +2377,15 @@
         <v>96</v>
       </c>
       <c r="G57" t="s">
-        <v>102</v>
+        <v>297</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B58" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G58" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -2397,7 +2393,7 @@
         <v>0</v>
       </c>
       <c r="B59" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
@@ -2405,7 +2401,7 @@
         <v>8</v>
       </c>
       <c r="B60" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
@@ -2413,7 +2409,7 @@
         <v>2</v>
       </c>
       <c r="B61" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
@@ -2421,7 +2417,7 @@
         <v>85</v>
       </c>
       <c r="L62" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -2429,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="B63" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
@@ -2437,7 +2433,7 @@
         <v>2</v>
       </c>
       <c r="B64" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:12" x14ac:dyDescent="0.2">
@@ -2445,7 +2441,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -2456,13 +2452,13 @@
         <v>6</v>
       </c>
       <c r="D66" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="I66" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="J66" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:12" x14ac:dyDescent="0.2">
@@ -2470,10 +2466,10 @@
         <v>8</v>
       </c>
       <c r="B67" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="I67" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.2">
@@ -2481,7 +2477,7 @@
         <v>2</v>
       </c>
       <c r="B68" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.2">
@@ -2489,7 +2485,7 @@
         <v>8</v>
       </c>
       <c r="B69" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.2">
@@ -2503,21 +2499,21 @@
         <v>96</v>
       </c>
       <c r="D70" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F70" t="s">
         <v>81</v>
       </c>
       <c r="I70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="L70" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B71" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.2">
@@ -2525,7 +2521,7 @@
         <v>0</v>
       </c>
       <c r="B72" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.2">
@@ -2533,10 +2529,10 @@
         <v>2</v>
       </c>
       <c r="B73" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G73" t="s">
-        <v>239</v>
+        <v>299</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -2544,13 +2540,13 @@
         <v>8</v>
       </c>
       <c r="B74" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D74" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G74" t="s">
-        <v>240</v>
+        <v>300</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -2558,7 +2554,7 @@
         <v>85</v>
       </c>
       <c r="D75" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F75" t="s">
         <v>81</v>
@@ -2572,7 +2568,7 @@
         <v>0</v>
       </c>
       <c r="B76" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.2">
@@ -2580,7 +2576,7 @@
         <v>0</v>
       </c>
       <c r="B77" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.2">
@@ -2588,13 +2584,13 @@
         <v>2</v>
       </c>
       <c r="B78" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="C78" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L78" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -2602,16 +2598,16 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="D79" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G79" t="s">
         <v>2</v>
       </c>
       <c r="L79" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -2619,22 +2615,22 @@
         <v>0</v>
       </c>
       <c r="B80" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="C80" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D80" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F80" t="s">
         <v>86</v>
       </c>
       <c r="G80" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
       <c r="L80" t="s">
-        <v>241</v>
+        <v>234</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
@@ -2666,16 +2662,16 @@
         <v>21</v>
       </c>
       <c r="B84" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D84" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F84" t="s">
         <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>214</v>
+        <v>301</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -2683,16 +2679,16 @@
         <v>2</v>
       </c>
       <c r="B85" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D85" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F85" t="s">
         <v>86</v>
       </c>
       <c r="G85" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -2708,7 +2704,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -2732,7 +2728,7 @@
         <v>8</v>
       </c>
       <c r="B90" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.2">
@@ -2740,7 +2736,7 @@
         <v>2</v>
       </c>
       <c r="B91" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.2">
@@ -2748,16 +2744,16 @@
         <v>0</v>
       </c>
       <c r="B92" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D92" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G92" t="s">
-        <v>213</v>
+        <v>298</v>
       </c>
       <c r="L92" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.2">
@@ -2765,7 +2761,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
@@ -2773,7 +2769,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
@@ -2781,7 +2777,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
@@ -2789,7 +2785,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
@@ -2797,7 +2793,7 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
@@ -2805,7 +2801,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
@@ -2813,7 +2809,7 @@
         <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
@@ -2821,12 +2817,12 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D101" t="s">
         <v>82</v>
@@ -2838,15 +2834,15 @@
         <v>80</v>
       </c>
       <c r="L101" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B102" t="s">
+        <v>130</v>
+      </c>
+      <c r="D102" t="s">
         <v>131</v>
-      </c>
-      <c r="D102" t="s">
-        <v>132</v>
       </c>
       <c r="F102" t="s">
         <v>86</v>
@@ -2860,10 +2856,10 @@
         <v>25</v>
       </c>
       <c r="C103" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="L103" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="104" spans="1:12" ht="171" x14ac:dyDescent="0.2">
@@ -2874,7 +2870,7 @@
         <v>27</v>
       </c>
       <c r="L104" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="105" spans="1:12" x14ac:dyDescent="0.2">
@@ -2882,7 +2878,10 @@
         <v>85</v>
       </c>
       <c r="C105" t="s">
-        <v>133</v>
+        <v>132</v>
+      </c>
+      <c r="L105" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
@@ -2890,7 +2889,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
@@ -2898,7 +2897,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
@@ -2914,7 +2913,7 @@
         <v>8</v>
       </c>
       <c r="B109" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.2">
@@ -2922,7 +2921,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
@@ -2930,7 +2929,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
@@ -2962,21 +2961,21 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="D115" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="D116" t="s">
         <v>82</v>
       </c>
       <c r="E116" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="F116" t="s">
         <v>81</v>
@@ -2987,7 +2986,7 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
@@ -2995,7 +2994,7 @@
         <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
@@ -3003,7 +3002,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
@@ -3011,7 +3010,7 @@
         <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>283</v>
+        <v>276</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
@@ -3019,7 +3018,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>284</v>
+        <v>277</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
@@ -3032,38 +3031,38 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="C123" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D123" t="s">
         <v>82</v>
       </c>
       <c r="E123" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="F123" t="s">
         <v>81</v>
       </c>
       <c r="L123" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>286</v>
+        <v>279</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>287</v>
+        <v>280</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
@@ -3071,20 +3070,20 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>288</v>
+        <v>281</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>289</v>
+        <v>282</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="D128" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.2">
@@ -3092,32 +3091,32 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>291</v>
+        <v>284</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
-        <v>294</v>
+        <v>287</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>295</v>
+        <v>288</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>292</v>
+        <v>285</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>293</v>
+        <v>286</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>296</v>
+        <v>289</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
@@ -3125,7 +3124,7 @@
         <v>0</v>
       </c>
       <c r="B135" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.2">
@@ -3133,13 +3132,13 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="D136" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E136" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.2">
@@ -3150,10 +3149,10 @@
         <v>32</v>
       </c>
       <c r="D137" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E137" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="F137" t="s">
         <v>81</v>
@@ -3164,10 +3163,10 @@
         <v>0</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D138" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F138" t="s">
         <v>86</v>
@@ -3181,7 +3180,7 @@
         <v>96</v>
       </c>
       <c r="D139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F139" t="s">
         <v>86</v>
@@ -3208,7 +3207,7 @@
         <v>0</v>
       </c>
       <c r="B142" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.2">
@@ -3232,7 +3231,7 @@
         <v>35</v>
       </c>
       <c r="B145" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.2">
@@ -3251,7 +3250,7 @@
         <v>39</v>
       </c>
       <c r="C147" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.2">
@@ -3291,7 +3290,7 @@
         <v>35</v>
       </c>
       <c r="B152" t="s">
-        <v>298</v>
+        <v>291</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
@@ -3302,7 +3301,7 @@
         <v>44</v>
       </c>
       <c r="C153" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.2">
@@ -3310,7 +3309,7 @@
         <v>35</v>
       </c>
       <c r="B154" t="s">
-        <v>299</v>
+        <v>292</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
@@ -3334,7 +3333,7 @@
         <v>35</v>
       </c>
       <c r="B157" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.2">
@@ -3342,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="B158" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.2">
@@ -3353,7 +3352,7 @@
         <v>49</v>
       </c>
       <c r="C159" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F159" t="s">
         <v>81</v>
@@ -3364,7 +3363,7 @@
         <v>35</v>
       </c>
       <c r="B160" t="s">
-        <v>300</v>
+        <v>293</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
@@ -3396,7 +3395,7 @@
         <v>2</v>
       </c>
       <c r="B164" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
     </row>
     <row r="165" spans="1:12" x14ac:dyDescent="0.2">
@@ -3404,7 +3403,7 @@
         <v>35</v>
       </c>
       <c r="B165" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.2">
@@ -3412,7 +3411,7 @@
         <v>35</v>
       </c>
       <c r="B166" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="167" spans="1:12" x14ac:dyDescent="0.2">
@@ -3423,16 +3422,16 @@
         <v>51</v>
       </c>
       <c r="D167" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="E167" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G167" t="s">
         <v>80</v>
       </c>
       <c r="L167" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.2">
@@ -3443,10 +3442,10 @@
         <v>52</v>
       </c>
       <c r="D168" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E168" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="F168" t="s">
         <v>81</v>
@@ -3455,7 +3454,7 @@
         <v>8</v>
       </c>
       <c r="L168" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="169" spans="1:12" x14ac:dyDescent="0.2">
@@ -3471,13 +3470,13 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="C170" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G170" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="171" spans="1:12" x14ac:dyDescent="0.2">
@@ -3496,7 +3495,7 @@
         <v>56</v>
       </c>
       <c r="C172" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="173" spans="1:12" x14ac:dyDescent="0.2">
@@ -3555,7 +3554,7 @@
         <v>63</v>
       </c>
       <c r="G179" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -3566,7 +3565,7 @@
         <v>64</v>
       </c>
       <c r="G180" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -3574,7 +3573,7 @@
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -3585,7 +3584,7 @@
         <v>65</v>
       </c>
       <c r="C182" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
@@ -3601,7 +3600,7 @@
         <v>0</v>
       </c>
       <c r="B184" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.2">
@@ -3673,7 +3672,7 @@
         <v>55</v>
       </c>
       <c r="B193" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
@@ -3681,7 +3680,7 @@
         <v>0</v>
       </c>
       <c r="B194" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
@@ -3705,7 +3704,7 @@
         <v>55</v>
       </c>
       <c r="B197" t="s">
-        <v>302</v>
+        <v>295</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
@@ -3713,21 +3712,21 @@
         <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="C198" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D198" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B199" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="G199" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
@@ -3735,7 +3734,7 @@
         <v>77</v>
       </c>
       <c r="D200" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F200" t="s">
         <v>81</v>
@@ -3746,20 +3745,20 @@
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B201" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B202" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B203" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D203" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
@@ -3767,10 +3766,10 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="L204" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">

--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12CD4C6F-7892-4C23-B125-DF3361DB237E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C77022-8478-414B-B12D-EC4E5FB0A568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="305">
   <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1142,10 +1142,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>叶苏明坚定地走进电影院，</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>&lt;中心文本&gt;&lt;淡入&gt;一天结束，两人回到公寓。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1239,6 +1235,18 @@
   </si>
   <si>
     <t>背景明度 &gt;&gt; 1.0</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新途/电影院</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒|叶苏明</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;叶苏明坚定地走进电影院</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1902,7 +1910,7 @@
         <v>249</v>
       </c>
       <c r="G15" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1916,7 +1924,7 @@
         <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -2307,7 +2315,7 @@
         <v>81</v>
       </c>
       <c r="G51" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -2377,7 +2385,7 @@
         <v>96</v>
       </c>
       <c r="G57" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -2385,7 +2393,7 @@
         <v>210</v>
       </c>
       <c r="G58" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -2532,7 +2540,7 @@
         <v>183</v>
       </c>
       <c r="G73" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -2546,7 +2554,7 @@
         <v>122</v>
       </c>
       <c r="G74" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -2627,7 +2635,7 @@
         <v>86</v>
       </c>
       <c r="G80" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="L80" t="s">
         <v>234</v>
@@ -2671,7 +2679,7 @@
         <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -2688,7 +2696,7 @@
         <v>86</v>
       </c>
       <c r="G85" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -2750,7 +2758,7 @@
         <v>125</v>
       </c>
       <c r="G92" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="L92" t="s">
         <v>208</v>
@@ -2881,7 +2889,7 @@
         <v>132</v>
       </c>
       <c r="L105" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
@@ -2980,6 +2988,9 @@
       <c r="F116" t="s">
         <v>81</v>
       </c>
+      <c r="G116" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A117" s="3" t="s">
@@ -2988,6 +2999,15 @@
       <c r="B117" t="s">
         <v>273</v>
       </c>
+      <c r="D117" t="s">
+        <v>302</v>
+      </c>
+      <c r="F117" t="s">
+        <v>86</v>
+      </c>
+      <c r="G117" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A118" s="3" t="s">
@@ -2995,6 +3015,9 @@
       </c>
       <c r="B118" t="s">
         <v>274</v>
+      </c>
+      <c r="L118" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.2">
@@ -3012,13 +3035,31 @@
       <c r="B120" t="s">
         <v>276</v>
       </c>
+      <c r="D120" t="s">
+        <v>302</v>
+      </c>
+      <c r="F120" t="s">
+        <v>86</v>
+      </c>
+      <c r="G120" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A121" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>277</v>
+        <v>304</v>
+      </c>
+      <c r="D121" t="s">
+        <v>82</v>
+      </c>
+      <c r="F121" t="s">
+        <v>81</v>
+      </c>
+      <c r="G121" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
@@ -3031,7 +3072,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C123" t="s">
         <v>133</v>
@@ -3054,7 +3095,7 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
@@ -3062,7 +3103,7 @@
         <v>2</v>
       </c>
       <c r="B125" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
@@ -3070,17 +3111,17 @@
         <v>0</v>
       </c>
       <c r="B126" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B127" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B128" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D128" t="s">
         <v>134</v>
@@ -3091,32 +3132,32 @@
         <v>0</v>
       </c>
       <c r="B129" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B130" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B131" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B132" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B133" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.2">
@@ -3132,7 +3173,7 @@
         <v>8</v>
       </c>
       <c r="B136" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="D136" t="s">
         <v>134</v>
@@ -3290,7 +3331,7 @@
         <v>35</v>
       </c>
       <c r="B152" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.2">
@@ -3309,7 +3350,7 @@
         <v>35</v>
       </c>
       <c r="B154" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.2">
@@ -3363,7 +3404,7 @@
         <v>35</v>
       </c>
       <c r="B160" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="161" spans="1:12" x14ac:dyDescent="0.2">
@@ -3470,7 +3511,7 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="C170" t="s">
         <v>144</v>
@@ -3704,7 +3745,7 @@
         <v>55</v>
       </c>
       <c r="B197" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">

--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C77022-8478-414B-B12D-EC4E5FB0A568}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D690487B-17F7-4518-BC11-737C15A4F63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15390" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14910" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="305">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="339">
   <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -932,10 +932,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>wait &gt;&gt; 4</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>都是——FoxTi，几个月前创建，因为一场事故，我们少了一位队员。幸存的两人一位是经验较为丰富的老手，一位……正在努力学习。总之——我们需要你带带这支还没成熟的队伍。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1146,22 +1142,10 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>漠寒，能不能在厕所外面等我……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>都说别看恐怖片……</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>在叶苏明洗澡的间隙，漠寒偷偷把行李箱中没拿出来的安眠药用团纸包着，几番挣扎，还是选择丢进垃圾桶，然后继续守在门口刷视频。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>待漠寒洗完澡，出来后发现叶苏明也在门口守着，不禁一笑。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>两人挤进卧室睡觉。</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1186,10 +1170,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>想着，叶苏明往漠寒那挪了挪。漠寒重重吸了口气，让叶苏明惊了一下。看漠寒舔了舔嘴唇，叶苏明才安下心来。</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>（我被老大帮助过太多次了，我该怎么回报他……？）</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
@@ -1247,6 +1227,162 @@
   </si>
   <si>
     <t>&lt;中心文本&gt;&lt;淡入&gt;叶苏明坚定地走进电影院</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>重置立绘</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>新途/电影</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>啊啊啊啊啊啊啊啊啊，老大！！！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大你说句话啊！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;你看，老大！我完全不怕！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;老大……屏幕里那个大块头感觉还有点……可爱……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;老大……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/怪物尖叫|音效/摔倒</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;—电影开播了—</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>都说了不要看了……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大，你为什么不害怕？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这不就是虚空兽吗？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>背景音乐循环 &gt;&gt; Airport Lounge &gt;&gt; True</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 8|背景音乐循环 &gt;&gt; Airport Lounge &gt;&gt; False|背景音乐进度 &gt;&gt; Airport Lounge &gt;&gt; 295</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒|叶苏明 &gt;&gt; 淡出</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大，能不能在厕所外面等我……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（哦，对了，我的安眠药……）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（让叶苏明看到了，他应该会想很多吧？）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（可我不吃药会睡不着的……）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（但他看到了更会睡不着吧？）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（他会想很多，况且，叶苏明本身也抑郁了……）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（到底为什么会这样？）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（算了，两个人睡得安心一点）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒偷偷打开行李箱。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>（就这样吧）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>他把安眠药用团纸包着，几番挣扎，还是选择丢进垃圾桶，然后继续守在门口刷视频。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>音效/拉拉链</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒|叶苏明_裸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>老大！</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>这么快？</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>还没等漠寒反应过来，叶苏明就帮漠寒在行李箱里拿好衣服了。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>你……好……我马上洗完。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>^漠寒 &gt;&gt; 淡出|叶苏明_裸</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>&lt;中心文本&gt;&lt;淡入&gt;待漠寒洗完澡，出来后发现叶苏明也在门口守着，不禁一笑。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>想着，叶苏明往漠寒那挪了挪。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>漠寒重重吸了口气，让叶苏明惊了一下。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>看漠寒舔了舔嘴唇，叶苏明才安下心来。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>wait &gt;&gt; 2</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -1692,7 +1828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF46EA-649E-46D2-A2F1-55ADFE170F2E}">
-  <dimension ref="A1:L205"/>
+  <dimension ref="A1:L239"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -1705,40 +1841,40 @@
   <sheetData>
     <row r="1" spans="1:12" ht="34.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="D1" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="E1" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="F1" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="G1" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="H1" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="I1" s="1" t="s">
         <v>245</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J1" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="L1" s="4" t="s">
         <v>246</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>255</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.2">
@@ -1907,10 +2043,10 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B15" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G15" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.2">
@@ -1918,13 +2054,13 @@
         <v>0</v>
       </c>
       <c r="B16" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D16" t="s">
         <v>90</v>
       </c>
       <c r="G16" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.2">
@@ -1952,7 +2088,7 @@
         <v>3</v>
       </c>
       <c r="B18" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C18" t="s">
         <v>94</v>
@@ -1961,7 +2097,7 @@
         <v>91</v>
       </c>
       <c r="L18" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.2">
@@ -1994,7 +2130,7 @@
         <v>2</v>
       </c>
       <c r="B21" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="D21" t="s">
         <v>89</v>
@@ -2025,7 +2161,7 @@
         <v>3</v>
       </c>
       <c r="B23" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="C23" t="s">
         <v>97</v>
@@ -2037,7 +2173,7 @@
         <v>81</v>
       </c>
       <c r="L23" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.2">
@@ -2089,10 +2225,10 @@
         <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="L28" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.2">
@@ -2122,7 +2258,7 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
@@ -2138,7 +2274,7 @@
         <v>103</v>
       </c>
       <c r="B33" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.2">
@@ -2256,7 +2392,7 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B47" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.2">
@@ -2278,7 +2414,7 @@
         <v>82</v>
       </c>
       <c r="E49" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F49" t="s">
         <v>81</v>
@@ -2309,13 +2445,13 @@
         <v>108</v>
       </c>
       <c r="E51" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F51" t="s">
         <v>81</v>
       </c>
       <c r="G51" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
@@ -2340,7 +2476,7 @@
         <v>114</v>
       </c>
       <c r="E53" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="I53" t="s">
         <v>115</v>
@@ -2368,7 +2504,7 @@
         <v>180</v>
       </c>
       <c r="E56" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I56" t="s">
         <v>118</v>
@@ -2385,7 +2521,7 @@
         <v>96</v>
       </c>
       <c r="G57" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
@@ -2393,7 +2529,7 @@
         <v>210</v>
       </c>
       <c r="G58" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
@@ -2419,13 +2555,16 @@
       <c r="B61" t="s">
         <v>169</v>
       </c>
+      <c r="L61" t="s">
+        <v>300</v>
+      </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" s="3" t="s">
         <v>85</v>
       </c>
       <c r="L62" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
@@ -2449,7 +2588,7 @@
         <v>8</v>
       </c>
       <c r="B65" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.2">
@@ -2540,7 +2679,7 @@
         <v>183</v>
       </c>
       <c r="G73" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.2">
@@ -2554,7 +2693,7 @@
         <v>122</v>
       </c>
       <c r="G74" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.2">
@@ -2598,7 +2737,7 @@
         <v>126</v>
       </c>
       <c r="L78" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.2">
@@ -2606,7 +2745,7 @@
         <v>0</v>
       </c>
       <c r="B79" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D79" t="s">
         <v>125</v>
@@ -2615,7 +2754,7 @@
         <v>2</v>
       </c>
       <c r="L79" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.2">
@@ -2635,10 +2774,10 @@
         <v>86</v>
       </c>
       <c r="G80" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="L80" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.2">
@@ -2679,7 +2818,7 @@
         <v>86</v>
       </c>
       <c r="G84" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.2">
@@ -2696,7 +2835,7 @@
         <v>86</v>
       </c>
       <c r="G85" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.2">
@@ -2712,7 +2851,7 @@
         <v>0</v>
       </c>
       <c r="B87" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.2">
@@ -2758,7 +2897,7 @@
         <v>125</v>
       </c>
       <c r="G92" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="L92" t="s">
         <v>208</v>
@@ -2769,7 +2908,7 @@
         <v>2</v>
       </c>
       <c r="B93" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.2">
@@ -2777,7 +2916,7 @@
         <v>8</v>
       </c>
       <c r="B94" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.2">
@@ -2785,7 +2924,7 @@
         <v>2</v>
       </c>
       <c r="B95" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.2">
@@ -2793,7 +2932,7 @@
         <v>8</v>
       </c>
       <c r="B96" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="97" spans="1:12" x14ac:dyDescent="0.2">
@@ -2801,7 +2940,7 @@
         <v>2</v>
       </c>
       <c r="B97" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.2">
@@ -2809,7 +2948,7 @@
         <v>0</v>
       </c>
       <c r="B98" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
     </row>
     <row r="99" spans="1:12" x14ac:dyDescent="0.2">
@@ -2817,7 +2956,7 @@
         <v>2</v>
       </c>
       <c r="B99" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.2">
@@ -2825,7 +2964,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
     </row>
     <row r="101" spans="1:12" x14ac:dyDescent="0.2">
@@ -2889,7 +3028,7 @@
         <v>132</v>
       </c>
       <c r="L105" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.2">
@@ -2897,7 +3036,7 @@
         <v>0</v>
       </c>
       <c r="B106" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="107" spans="1:12" x14ac:dyDescent="0.2">
@@ -2905,7 +3044,7 @@
         <v>8</v>
       </c>
       <c r="B107" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.2">
@@ -2929,7 +3068,7 @@
         <v>2</v>
       </c>
       <c r="B110" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="111" spans="1:12" x14ac:dyDescent="0.2">
@@ -2937,7 +3076,7 @@
         <v>8</v>
       </c>
       <c r="B111" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.2">
@@ -2969,21 +3108,24 @@
         <v>0</v>
       </c>
       <c r="B115" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="D115" t="s">
         <v>131</v>
       </c>
+      <c r="E115" t="s">
+        <v>231</v>
+      </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B116" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D116" t="s">
         <v>82</v>
       </c>
       <c r="E116" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="F116" t="s">
         <v>81</v>
@@ -2997,16 +3139,16 @@
         <v>0</v>
       </c>
       <c r="B117" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D117" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F117" t="s">
         <v>86</v>
       </c>
       <c r="G117" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.2">
@@ -3014,7 +3156,7 @@
         <v>2</v>
       </c>
       <c r="B118" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L118" t="s">
         <v>208</v>
@@ -3025,7 +3167,7 @@
         <v>8</v>
       </c>
       <c r="B119" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.2">
@@ -3033,16 +3175,16 @@
         <v>2</v>
       </c>
       <c r="B120" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D120" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="F120" t="s">
         <v>86</v>
       </c>
       <c r="G120" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.2">
@@ -3050,7 +3192,7 @@
         <v>0</v>
       </c>
       <c r="B121" t="s">
-        <v>304</v>
+        <v>299</v>
       </c>
       <c r="D121" t="s">
         <v>82</v>
@@ -3063,8 +3205,11 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A122" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B122" t="s">
-        <v>6</v>
+        <v>309</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
@@ -3072,22 +3217,7 @@
         <v>0</v>
       </c>
       <c r="B123" t="s">
-        <v>277</v>
-      </c>
-      <c r="C123" t="s">
-        <v>133</v>
-      </c>
-      <c r="D123" t="s">
-        <v>82</v>
-      </c>
-      <c r="E123" t="s">
-        <v>220</v>
-      </c>
-      <c r="F123" t="s">
-        <v>81</v>
-      </c>
-      <c r="L123" t="s">
-        <v>222</v>
+        <v>302</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
@@ -3095,711 +3225,750 @@
         <v>8</v>
       </c>
       <c r="B124" t="s">
-        <v>278</v>
+        <v>305</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B125" t="s">
-        <v>279</v>
+        <v>302</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B126" t="s">
-        <v>280</v>
+        <v>306</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A127" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B127" t="s">
-        <v>281</v>
+        <v>302</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A128" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B128" t="s">
-        <v>282</v>
+        <v>307</v>
       </c>
       <c r="D128" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="129" spans="1:6" x14ac:dyDescent="0.2">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B129" t="s">
-        <v>283</v>
-      </c>
-    </row>
-    <row r="130" spans="1:6" x14ac:dyDescent="0.2">
+        <v>303</v>
+      </c>
+      <c r="C129" t="s">
+        <v>308</v>
+      </c>
+      <c r="D129" t="s">
+        <v>301</v>
+      </c>
+      <c r="F129" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="130" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A130" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B130" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="131" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A131" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B131" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="132" spans="1:6" x14ac:dyDescent="0.2">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="132" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A132" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B132" t="s">
-        <v>284</v>
-      </c>
-    </row>
-    <row r="133" spans="1:6" x14ac:dyDescent="0.2">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="133" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A133" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B133" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="134" spans="1:6" x14ac:dyDescent="0.2">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="134" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A134" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B134" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="135" spans="1:6" x14ac:dyDescent="0.2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="135" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A135" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B135" t="s">
-        <v>195</v>
-      </c>
-    </row>
-    <row r="136" spans="1:6" x14ac:dyDescent="0.2">
+        <v>312</v>
+      </c>
+      <c r="D135" t="s">
+        <v>301</v>
+      </c>
+      <c r="L135" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="136" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A136" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B136" t="s">
-        <v>289</v>
+        <v>85</v>
+      </c>
+      <c r="C136" t="s">
+        <v>133</v>
       </c>
       <c r="D136" t="s">
-        <v>134</v>
+        <v>82</v>
       </c>
       <c r="E136" t="s">
+        <v>236</v>
+      </c>
+      <c r="F136" t="s">
+        <v>81</v>
+      </c>
+      <c r="L136" t="s">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="137" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A137" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B137" t="s">
+        <v>276</v>
+      </c>
+      <c r="D137" t="s">
+        <v>82</v>
+      </c>
+      <c r="E137" t="s">
         <v>220</v>
-      </c>
-    </row>
-    <row r="137" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A137" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B137" t="s">
-        <v>32</v>
-      </c>
-      <c r="D137" t="s">
-        <v>135</v>
-      </c>
-      <c r="E137" t="s">
-        <v>236</v>
       </c>
       <c r="F137" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="138" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="G137" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="138" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A138" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B138" t="s">
-        <v>137</v>
+        <v>316</v>
       </c>
       <c r="D138" t="s">
-        <v>136</v>
-      </c>
-      <c r="F138" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="139" spans="1:6" x14ac:dyDescent="0.2">
+        <v>134</v>
+      </c>
+      <c r="G138" t="s">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="139" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A139" s="3" t="s">
-        <v>85</v>
+        <v>2</v>
+      </c>
+      <c r="B139" t="s">
+        <v>277</v>
       </c>
       <c r="C139" t="s">
         <v>96</v>
       </c>
-      <c r="D139" t="s">
+      <c r="G139" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="140" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B140" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B141" t="s">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B142" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B143" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B144" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B145" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B146" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A147" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B147" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A148" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B148" t="s">
+        <v>324</v>
+      </c>
+      <c r="C148" t="s">
+        <v>327</v>
+      </c>
+      <c r="L148" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A149" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B149" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A150" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B150" t="s">
+        <v>326</v>
+      </c>
+      <c r="D150" t="s">
+        <v>134</v>
+      </c>
+      <c r="G150" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A151" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D151" t="s">
+        <v>82</v>
+      </c>
+      <c r="F151" t="s">
+        <v>81</v>
+      </c>
+      <c r="G151" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A152" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B152" t="s">
+        <v>329</v>
+      </c>
+      <c r="D152" t="s">
+        <v>134</v>
+      </c>
+      <c r="G152" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A153" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B153" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A154" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B154" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A155" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B155" t="s">
+        <v>332</v>
+      </c>
+      <c r="G155" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A156" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D156" t="s">
+        <v>134</v>
+      </c>
+      <c r="G156" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A157" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D157" t="s">
+        <v>82</v>
+      </c>
+      <c r="F157" t="s">
+        <v>81</v>
+      </c>
+      <c r="G157" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A158" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B158" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B159" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B160" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B161" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B162" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B163" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B164" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B165" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B166" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="B167" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A168" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B168" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A169" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B169" t="s">
+        <v>284</v>
+      </c>
+      <c r="E169" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A170" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B170" t="s">
+        <v>302</v>
+      </c>
+      <c r="D170" t="s">
+        <v>82</v>
+      </c>
+      <c r="F170" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A171" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B171" t="s">
+        <v>32</v>
+      </c>
+      <c r="D171" t="s">
+        <v>135</v>
+      </c>
+      <c r="E171" t="s">
+        <v>235</v>
+      </c>
+      <c r="F171" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A172" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B172" t="s">
+        <v>137</v>
+      </c>
+      <c r="D172" t="s">
+        <v>136</v>
+      </c>
+      <c r="F172" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A173" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C173" t="s">
+        <v>96</v>
+      </c>
+      <c r="D173" t="s">
         <v>138</v>
       </c>
-      <c r="F139" t="s">
+      <c r="F173" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="140" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A140" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B140" t="s">
+    <row r="174" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A174" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B174" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="141" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A141" s="3" t="s">
+    <row r="175" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A175" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B141" t="s">
+      <c r="B175" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="142" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A142" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B142" t="s">
+    <row r="176" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A176" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B176" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="143" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A143" s="3" t="s">
+    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A177" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B143" t="s">
+      <c r="B177" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="144" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A144" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B144" t="s">
+    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B178" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A145" s="3" t="s">
+    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A179" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B145" t="s">
+      <c r="B179" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="146" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A146" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B146" t="s">
+    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B180" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="147" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A147" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B147" t="s">
+    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A181" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B181" t="s">
         <v>39</v>
       </c>
-      <c r="C147" t="s">
+      <c r="C181" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A148" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B148" t="s">
+    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A182" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B182" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A149" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B149" t="s">
+    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A183" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B183" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="150" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A150" s="3" t="s">
+    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A184" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B150" t="s">
+      <c r="B184" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="151" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A151" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B151" t="s">
+    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B185" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="152" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A152" s="3" t="s">
+    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A186" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B152" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="153" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B153" t="s">
+      <c r="B186" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A187" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B187" t="s">
         <v>44</v>
       </c>
-      <c r="C153" t="s">
+      <c r="C187" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="154" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
+    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A188" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B154" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="155" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B155" t="s">
+      <c r="B188" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A189" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B189" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="156" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B156" t="s">
+    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A190" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B190" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="157" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="s">
+    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A191" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B157" t="s">
+      <c r="B191" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A192" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B192" t="s">
         <v>223</v>
-      </c>
-    </row>
-    <row r="158" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B158" t="s">
-        <v>224</v>
-      </c>
-    </row>
-    <row r="159" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A159" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B159" t="s">
-        <v>49</v>
-      </c>
-      <c r="C159" t="s">
-        <v>141</v>
-      </c>
-      <c r="F159" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="160" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A160" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B160" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="161" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A161" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B161" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="162" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A162" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B162" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="163" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A163" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B163" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="164" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A164" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B164" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="165" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A165" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B165" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="166" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A166" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B166" t="s">
-        <v>199</v>
-      </c>
-    </row>
-    <row r="167" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A167" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B167" t="s">
-        <v>51</v>
-      </c>
-      <c r="D167" t="s">
-        <v>138</v>
-      </c>
-      <c r="E167" t="s">
-        <v>236</v>
-      </c>
-      <c r="G167" t="s">
-        <v>80</v>
-      </c>
-      <c r="L167" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="168" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A168" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B168" t="s">
-        <v>52</v>
-      </c>
-      <c r="D168" t="s">
-        <v>143</v>
-      </c>
-      <c r="E168" t="s">
-        <v>237</v>
-      </c>
-      <c r="F168" t="s">
-        <v>81</v>
-      </c>
-      <c r="G168" t="s">
-        <v>8</v>
-      </c>
-      <c r="L168" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="169" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B169" t="s">
-        <v>53</v>
-      </c>
-      <c r="G169" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="170" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A170" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B170" t="s">
-        <v>293</v>
-      </c>
-      <c r="C170" t="s">
-        <v>144</v>
-      </c>
-      <c r="G170" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="171" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A171" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B171" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="172" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A172" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B172" t="s">
-        <v>56</v>
-      </c>
-      <c r="C172" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="173" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A173" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B173" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="174" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A174" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B174" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="175" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A175" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B175" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="176" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A176" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B176" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A177" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B177" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B178" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A179" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B179" t="s">
-        <v>63</v>
-      </c>
-      <c r="G179" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B180" t="s">
-        <v>64</v>
-      </c>
-      <c r="G180" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A181" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B181" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A182" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B182" t="s">
-        <v>65</v>
-      </c>
-      <c r="C182" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A183" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B183" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A184" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B184" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B185" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A186" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B186" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A187" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B187" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A188" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B188" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A189" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B189" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A190" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B190" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="191" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A191" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B191" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A192" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B192" t="s">
-        <v>74</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="B193" t="s">
-        <v>202</v>
+        <v>49</v>
+      </c>
+      <c r="C193" t="s">
+        <v>141</v>
+      </c>
+      <c r="F193" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A194" s="3" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B194" t="s">
-        <v>203</v>
+        <v>287</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A195" s="3" t="s">
-        <v>55</v>
+        <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A196" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>76</v>
+        <v>50</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A197" s="3" t="s">
-        <v>55</v>
+        <v>35</v>
       </c>
       <c r="B197" t="s">
-        <v>294</v>
+        <v>48</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B198" t="s">
-        <v>214</v>
-      </c>
-      <c r="C198" t="s">
-        <v>146</v>
-      </c>
-      <c r="D198" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A199" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B199" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A200" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B200" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A201" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B201" t="s">
+        <v>51</v>
+      </c>
+      <c r="D201" t="s">
+        <v>138</v>
+      </c>
+      <c r="E201" t="s">
+        <v>235</v>
+      </c>
+      <c r="G201" t="s">
+        <v>80</v>
+      </c>
+      <c r="L201" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A202" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B202" t="s">
+        <v>52</v>
+      </c>
+      <c r="D202" t="s">
         <v>143</v>
       </c>
-    </row>
-    <row r="199" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B199" t="s">
-        <v>215</v>
-      </c>
-      <c r="G199" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="200" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B200" t="s">
-        <v>77</v>
-      </c>
-      <c r="D200" t="s">
-        <v>147</v>
-      </c>
-      <c r="F200" t="s">
+      <c r="E202" t="s">
+        <v>236</v>
+      </c>
+      <c r="F202" t="s">
         <v>81</v>
       </c>
-      <c r="G200" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="201" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B201" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="202" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B202" t="s">
-        <v>205</v>
+      <c r="G202" t="s">
+        <v>8</v>
+      </c>
+      <c r="L202" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B203" t="s">
-        <v>206</v>
-      </c>
-      <c r="D203" t="s">
-        <v>147</v>
+        <v>53</v>
+      </c>
+      <c r="G203" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
@@ -3807,14 +3976,310 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
+        <v>288</v>
+      </c>
+      <c r="C204" t="s">
+        <v>144</v>
+      </c>
+      <c r="G204" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A205" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B205" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="206" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A206" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B206" t="s">
+        <v>56</v>
+      </c>
+      <c r="C206" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="207" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A207" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B207" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="208" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A208" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B208" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A209" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B209" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A210" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B210" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A211" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B211" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A212" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B212" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A213" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B213" t="s">
+        <v>63</v>
+      </c>
+      <c r="G213" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A214" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B214" t="s">
+        <v>64</v>
+      </c>
+      <c r="G214" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A215" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B215" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A216" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B216" t="s">
+        <v>65</v>
+      </c>
+      <c r="C216" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A217" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B217" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A218" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B218" t="s">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A219" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B219" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A220" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B220" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A221" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B221" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A222" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B222" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A223" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B223" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A224" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B224" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="225" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A225" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B225" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="226" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A226" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B226" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="227" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A227" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B227" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="228" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A228" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B228" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="229" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A229" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B229" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="230" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A230" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B230" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="231" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A231" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B231" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="232" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A232" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B232" t="s">
+        <v>214</v>
+      </c>
+      <c r="C232" t="s">
+        <v>146</v>
+      </c>
+      <c r="D232" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="233" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B233" t="s">
+        <v>215</v>
+      </c>
+      <c r="G233" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B234" t="s">
+        <v>77</v>
+      </c>
+      <c r="D234" t="s">
+        <v>147</v>
+      </c>
+      <c r="F234" t="s">
+        <v>81</v>
+      </c>
+      <c r="G234" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B235" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B236" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="B237" t="s">
+        <v>206</v>
+      </c>
+      <c r="D237" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A238" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B238" t="s">
         <v>207</v>
       </c>
-      <c r="L204" t="s">
+      <c r="L238" t="s">
         <v>209</v>
       </c>
     </row>
-    <row r="205" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L205" t="s">
+    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="L239" t="s">
         <v>78</v>
       </c>
     </row>

--- a/Assets/StreamingAssets/Chapter/Chapter1.xlsx
+++ b/Assets/StreamingAssets/Chapter/Chapter1.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProject\shina\Assets\StreamingAssets\Chapter\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D690487B-17F7-4518-BC11-737C15A4F63D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C8EF708-3999-4851-8F95-8BE76CADA7E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14910" xr2:uid="{93CEB1B2-C3AD-4226-8194-AA135A927779}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="653" uniqueCount="339">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="641" uniqueCount="336">
   <si>
     <t>&amp;VO</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -1247,18 +1247,6 @@
   </si>
   <si>
     <t>老大你说句话啊！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;你看，老大！我完全不怕！</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;老大……屏幕里那个大块头感觉还有点……可爱……</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>&lt;中心文本&gt;&lt;淡入&gt;老大……</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
@@ -1828,7 +1816,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D3CF46EA-649E-46D2-A2F1-55ADFE170F2E}">
-  <dimension ref="A1:L239"/>
+  <dimension ref="A1:L233"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.25" style="3" customWidth="1"/>
@@ -3209,279 +3197,297 @@
         <v>0</v>
       </c>
       <c r="B122" t="s">
-        <v>309</v>
+        <v>306</v>
+      </c>
+      <c r="D122" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A123" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B123" t="s">
-        <v>302</v>
+        <v>303</v>
+      </c>
+      <c r="C123" t="s">
+        <v>305</v>
+      </c>
+      <c r="D123" t="s">
+        <v>301</v>
+      </c>
+      <c r="F123" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A124" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B124" t="s">
-        <v>305</v>
+        <v>6</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A125" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B125" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A126" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B126" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A127" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B127" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A128" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B128" t="s">
-        <v>307</v>
-      </c>
-      <c r="D128" t="s">
-        <v>82</v>
+        <v>6</v>
       </c>
     </row>
     <row r="129" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A129" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B129" t="s">
-        <v>303</v>
-      </c>
-      <c r="C129" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D129" t="s">
         <v>301</v>
       </c>
-      <c r="F129" t="s">
-        <v>86</v>
+      <c r="L129" t="s">
+        <v>310</v>
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A130" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B130" t="s">
-        <v>6</v>
+        <v>85</v>
+      </c>
+      <c r="C130" t="s">
+        <v>133</v>
+      </c>
+      <c r="D130" t="s">
+        <v>82</v>
+      </c>
+      <c r="E130" t="s">
+        <v>236</v>
+      </c>
+      <c r="F130" t="s">
+        <v>81</v>
+      </c>
+      <c r="L130" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="131" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A131" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B131" t="s">
-        <v>304</v>
+        <v>276</v>
+      </c>
+      <c r="D131" t="s">
+        <v>82</v>
+      </c>
+      <c r="E131" t="s">
+        <v>220</v>
+      </c>
+      <c r="F131" t="s">
+        <v>81</v>
+      </c>
+      <c r="G131" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A132" s="3" t="s">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B132" t="s">
-        <v>310</v>
+        <v>313</v>
+      </c>
+      <c r="D132" t="s">
+        <v>134</v>
+      </c>
+      <c r="G132" t="s">
+        <v>298</v>
       </c>
     </row>
     <row r="133" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A133" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B133" t="s">
-        <v>311</v>
+        <v>277</v>
+      </c>
+      <c r="C133" t="s">
+        <v>96</v>
+      </c>
+      <c r="G133" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A134" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B134" t="s">
-        <v>6</v>
+        <v>314</v>
       </c>
     </row>
     <row r="135" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A135" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B135" t="s">
-        <v>312</v>
-      </c>
-      <c r="D135" t="s">
-        <v>301</v>
-      </c>
-      <c r="L135" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A136" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C136" t="s">
-        <v>133</v>
-      </c>
-      <c r="D136" t="s">
-        <v>82</v>
-      </c>
-      <c r="E136" t="s">
-        <v>236</v>
-      </c>
-      <c r="F136" t="s">
-        <v>81</v>
-      </c>
-      <c r="L136" t="s">
-        <v>314</v>
+      <c r="B136" t="s">
+        <v>316</v>
       </c>
     </row>
     <row r="137" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A137" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B137" t="s">
-        <v>276</v>
-      </c>
-      <c r="D137" t="s">
-        <v>82</v>
-      </c>
-      <c r="E137" t="s">
-        <v>220</v>
-      </c>
-      <c r="F137" t="s">
-        <v>81</v>
-      </c>
-      <c r="G137" t="s">
-        <v>80</v>
+        <v>317</v>
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A138" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="B138" t="s">
-        <v>316</v>
-      </c>
-      <c r="D138" t="s">
-        <v>134</v>
-      </c>
-      <c r="G138" t="s">
-        <v>298</v>
+        <v>318</v>
       </c>
     </row>
     <row r="139" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A139" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B139" t="s">
-        <v>277</v>
-      </c>
-      <c r="C139" t="s">
-        <v>96</v>
-      </c>
-      <c r="G139" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B140" t="s">
-        <v>317</v>
+        <v>6</v>
       </c>
     </row>
     <row r="141" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A141" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B141" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A142" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B142" t="s">
-        <v>319</v>
+        <v>321</v>
+      </c>
+      <c r="C142" t="s">
+        <v>324</v>
+      </c>
+      <c r="L142" t="s">
+        <v>335</v>
       </c>
     </row>
     <row r="143" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A143" s="3" t="s">
+        <v>2</v>
+      </c>
       <c r="B143" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A144" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B144" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="145" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B145" t="s">
-        <v>322</v>
-      </c>
-    </row>
-    <row r="146" spans="1:12" x14ac:dyDescent="0.2">
+        <v>323</v>
+      </c>
+      <c r="D144" t="s">
+        <v>134</v>
+      </c>
+      <c r="G144" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A145" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="D145" t="s">
+        <v>82</v>
+      </c>
+      <c r="F145" t="s">
+        <v>81</v>
+      </c>
+      <c r="G145" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A146" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B146" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="147" spans="1:12" x14ac:dyDescent="0.2">
+        <v>326</v>
+      </c>
+      <c r="D146" t="s">
+        <v>134</v>
+      </c>
+      <c r="G146" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A147" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B147" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="148" spans="1:12" x14ac:dyDescent="0.2">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A148" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B148" t="s">
-        <v>324</v>
-      </c>
-      <c r="C148" t="s">
-        <v>327</v>
-      </c>
-      <c r="L148" t="s">
-        <v>338</v>
-      </c>
-    </row>
-    <row r="149" spans="1:12" x14ac:dyDescent="0.2">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A149" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B149" t="s">
+        <v>329</v>
+      </c>
+      <c r="G149" t="s">
         <v>325</v>
       </c>
     </row>
-    <row r="150" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A150" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B150" t="s">
-        <v>326</v>
+        <v>85</v>
       </c>
       <c r="D150" t="s">
         <v>134</v>
       </c>
       <c r="G150" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="151" spans="1:12" x14ac:dyDescent="0.2">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A151" s="3" t="s">
         <v>85</v>
       </c>
@@ -3495,142 +3501,151 @@
         <v>80</v>
       </c>
     </row>
-    <row r="152" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A152" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B152" t="s">
-        <v>329</v>
-      </c>
-      <c r="D152" t="s">
-        <v>134</v>
-      </c>
-      <c r="G152" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="153" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A153" s="3" t="s">
-        <v>2</v>
-      </c>
+        <v>331</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B153" t="s">
-        <v>330</v>
-      </c>
-    </row>
-    <row r="154" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A154" s="3" t="s">
-        <v>0</v>
-      </c>
+        <v>278</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B154" t="s">
-        <v>331</v>
-      </c>
-    </row>
-    <row r="155" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A155" s="3" t="s">
-        <v>2</v>
-      </c>
+        <v>279</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B155" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B156" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B157" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B158" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B159" t="s">
         <v>332</v>
       </c>
-      <c r="G155" t="s">
-        <v>328</v>
-      </c>
-    </row>
-    <row r="156" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A156" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D156" t="s">
-        <v>134</v>
-      </c>
-      <c r="G156" t="s">
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="B160" t="s">
         <v>333</v>
-      </c>
-    </row>
-    <row r="157" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A157" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="D157" t="s">
-        <v>82</v>
-      </c>
-      <c r="F157" t="s">
-        <v>81</v>
-      </c>
-      <c r="G157" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="158" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A158" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B158" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="159" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B159" t="s">
-        <v>278</v>
-      </c>
-    </row>
-    <row r="160" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B160" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.2">
       <c r="B161" t="s">
-        <v>282</v>
+        <v>334</v>
       </c>
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A162" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B162" t="s">
-        <v>283</v>
+        <v>195</v>
       </c>
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A163" s="3" t="s">
+        <v>8</v>
+      </c>
       <c r="B163" t="s">
-        <v>280</v>
+        <v>284</v>
+      </c>
+      <c r="E163" t="s">
+        <v>220</v>
       </c>
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A164" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B164" t="s">
-        <v>281</v>
+        <v>302</v>
+      </c>
+      <c r="D164" t="s">
+        <v>82</v>
+      </c>
+      <c r="F164" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A165" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B165" t="s">
-        <v>335</v>
+        <v>32</v>
+      </c>
+      <c r="D165" t="s">
+        <v>135</v>
+      </c>
+      <c r="E165" t="s">
+        <v>235</v>
+      </c>
+      <c r="F165" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A166" s="3" t="s">
+        <v>0</v>
+      </c>
       <c r="B166" t="s">
-        <v>336</v>
+        <v>137</v>
+      </c>
+      <c r="D166" t="s">
+        <v>136</v>
+      </c>
+      <c r="F166" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="B167" t="s">
-        <v>337</v>
+      <c r="A167" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C167" t="s">
+        <v>96</v>
+      </c>
+      <c r="D167" t="s">
+        <v>138</v>
+      </c>
+      <c r="F167" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A168" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B168" t="s">
-        <v>195</v>
+        <v>33</v>
       </c>
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A169" s="3" t="s">
-        <v>8</v>
+        <v>35</v>
       </c>
       <c r="B169" t="s">
-        <v>284</v>
-      </c>
-      <c r="E169" t="s">
-        <v>220</v>
+        <v>34</v>
       </c>
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.2">
@@ -3638,58 +3653,31 @@
         <v>0</v>
       </c>
       <c r="B170" t="s">
-        <v>302</v>
-      </c>
-      <c r="D170" t="s">
-        <v>82</v>
-      </c>
-      <c r="F170" t="s">
-        <v>81</v>
+        <v>197</v>
       </c>
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A171" s="3" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B171" t="s">
-        <v>32</v>
-      </c>
-      <c r="D171" t="s">
-        <v>135</v>
-      </c>
-      <c r="E171" t="s">
-        <v>235</v>
-      </c>
-      <c r="F171" t="s">
-        <v>81</v>
+        <v>36</v>
       </c>
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A172" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B172" t="s">
-        <v>137</v>
-      </c>
-      <c r="D172" t="s">
-        <v>136</v>
-      </c>
-      <c r="F172" t="s">
-        <v>86</v>
+        <v>37</v>
       </c>
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A173" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C173" t="s">
-        <v>96</v>
-      </c>
-      <c r="D173" t="s">
-        <v>138</v>
-      </c>
-      <c r="F173" t="s">
-        <v>86</v>
+        <v>35</v>
+      </c>
+      <c r="B173" t="s">
+        <v>196</v>
       </c>
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.2">
@@ -3697,171 +3685,171 @@
         <v>2</v>
       </c>
       <c r="B174" t="s">
-        <v>33</v>
+        <v>38</v>
       </c>
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A175" s="3" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B175" t="s">
-        <v>34</v>
+        <v>39</v>
+      </c>
+      <c r="C175" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A176" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B176" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="177" spans="1:3" x14ac:dyDescent="0.2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A177" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B177" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A178" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B177" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="178" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A178" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B178" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="179" spans="1:3" x14ac:dyDescent="0.2">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A179" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B179" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A180" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B179" t="s">
-        <v>196</v>
-      </c>
-    </row>
-    <row r="180" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A180" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B180" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="181" spans="1:3" x14ac:dyDescent="0.2">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A181" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B181" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="C181" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="182" spans="1:3" x14ac:dyDescent="0.2">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A182" s="3" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B182" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="183" spans="1:3" x14ac:dyDescent="0.2">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A183" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B183" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="184" spans="1:3" x14ac:dyDescent="0.2">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A184" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B184" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A185" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B184" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="185" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A185" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B185" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="186" spans="1:3" x14ac:dyDescent="0.2">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A186" s="3" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B186" t="s">
-        <v>285</v>
-      </c>
-    </row>
-    <row r="187" spans="1:3" x14ac:dyDescent="0.2">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A187" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B187" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C187" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="188" spans="1:3" x14ac:dyDescent="0.2">
+        <v>141</v>
+      </c>
+      <c r="F187" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A188" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B188" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="189" spans="1:3" x14ac:dyDescent="0.2">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A189" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B189" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="190" spans="1:3" x14ac:dyDescent="0.2">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A190" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B190" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="191" spans="1:3" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A191" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B191" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="192" spans="1:3" x14ac:dyDescent="0.2">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A192" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B192" t="s">
-        <v>223</v>
+        <v>198</v>
       </c>
     </row>
     <row r="193" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A193" s="3" t="s">
-        <v>0</v>
+        <v>35</v>
       </c>
       <c r="B193" t="s">
-        <v>49</v>
-      </c>
-      <c r="C193" t="s">
-        <v>141</v>
-      </c>
-      <c r="F193" t="s">
-        <v>81</v>
+        <v>142</v>
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.2">
@@ -3869,7 +3857,7 @@
         <v>35</v>
       </c>
       <c r="B194" t="s">
-        <v>287</v>
+        <v>199</v>
       </c>
     </row>
     <row r="195" spans="1:12" x14ac:dyDescent="0.2">
@@ -3877,7 +3865,19 @@
         <v>2</v>
       </c>
       <c r="B195" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="D195" t="s">
+        <v>138</v>
+      </c>
+      <c r="E195" t="s">
+        <v>235</v>
+      </c>
+      <c r="G195" t="s">
+        <v>80</v>
+      </c>
+      <c r="L195" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.2">
@@ -3885,59 +3885,71 @@
         <v>0</v>
       </c>
       <c r="B196" t="s">
-        <v>50</v>
+        <v>52</v>
+      </c>
+      <c r="D196" t="s">
+        <v>143</v>
+      </c>
+      <c r="E196" t="s">
+        <v>236</v>
+      </c>
+      <c r="F196" t="s">
+        <v>81</v>
+      </c>
+      <c r="G196" t="s">
+        <v>8</v>
+      </c>
+      <c r="L196" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="197" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A197" s="3" t="s">
-        <v>35</v>
-      </c>
       <c r="B197" t="s">
-        <v>48</v>
+        <v>53</v>
+      </c>
+      <c r="G197" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A198" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B198" t="s">
-        <v>198</v>
+        <v>288</v>
+      </c>
+      <c r="C198" t="s">
+        <v>144</v>
+      </c>
+      <c r="G198" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="199" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A199" s="3" t="s">
-        <v>35</v>
+        <v>55</v>
       </c>
       <c r="B199" t="s">
-        <v>142</v>
+        <v>54</v>
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A200" s="3" t="s">
-        <v>35</v>
+        <v>0</v>
       </c>
       <c r="B200" t="s">
-        <v>199</v>
+        <v>56</v>
+      </c>
+      <c r="C200" t="s">
+        <v>139</v>
       </c>
     </row>
     <row r="201" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A201" s="3" t="s">
-        <v>2</v>
+        <v>55</v>
       </c>
       <c r="B201" t="s">
-        <v>51</v>
-      </c>
-      <c r="D201" t="s">
-        <v>138</v>
-      </c>
-      <c r="E201" t="s">
-        <v>235</v>
-      </c>
-      <c r="G201" t="s">
-        <v>80</v>
-      </c>
-      <c r="L201" t="s">
-        <v>209</v>
+        <v>57</v>
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.2">
@@ -3945,30 +3957,15 @@
         <v>0</v>
       </c>
       <c r="B202" t="s">
-        <v>52</v>
-      </c>
-      <c r="D202" t="s">
-        <v>143</v>
-      </c>
-      <c r="E202" t="s">
-        <v>236</v>
-      </c>
-      <c r="F202" t="s">
-        <v>81</v>
-      </c>
-      <c r="G202" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A203" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L202" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="203" spans="1:12" x14ac:dyDescent="0.2">
       <c r="B203" t="s">
-        <v>53</v>
-      </c>
-      <c r="G203" t="s">
-        <v>8</v>
+        <v>60</v>
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.2">
@@ -3976,13 +3973,7 @@
         <v>0</v>
       </c>
       <c r="B204" t="s">
-        <v>288</v>
-      </c>
-      <c r="C204" t="s">
-        <v>144</v>
-      </c>
-      <c r="G204" t="s">
-        <v>212</v>
+        <v>59</v>
       </c>
     </row>
     <row r="205" spans="1:12" x14ac:dyDescent="0.2">
@@ -3990,18 +3981,15 @@
         <v>55</v>
       </c>
       <c r="B205" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A206" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B206" t="s">
-        <v>56</v>
-      </c>
-      <c r="C206" t="s">
-        <v>139</v>
+        <v>62</v>
       </c>
     </row>
     <row r="207" spans="1:12" x14ac:dyDescent="0.2">
@@ -4009,152 +3997,152 @@
         <v>55</v>
       </c>
       <c r="B207" t="s">
-        <v>57</v>
+        <v>63</v>
+      </c>
+      <c r="G207" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A208" s="3" t="s">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B208" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.2">
+        <v>64</v>
+      </c>
+      <c r="G208" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="209" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A209" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B209" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.2">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="210" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A210" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B210" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.2">
+        <v>65</v>
+      </c>
+      <c r="C210" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="211" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A211" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B211" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="212" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A212" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B212" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.2">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="213" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A213" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B213" t="s">
-        <v>63</v>
-      </c>
-      <c r="G213" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="214" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A214" s="3" t="s">
         <v>2</v>
       </c>
       <c r="B214" t="s">
-        <v>64</v>
-      </c>
-      <c r="G214" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.2">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="215" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A215" s="3" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B215" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="216" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A216" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B216" t="s">
-        <v>65</v>
-      </c>
-      <c r="C216" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="217" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A217" s="3" t="s">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="B217" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.2">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="218" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A218" s="3" t="s">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="B218" t="s">
-        <v>201</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.2">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="219" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A219" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B219" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="220" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A220" s="3" t="s">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B220" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.2">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="221" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A221" s="3" t="s">
         <v>55</v>
       </c>
       <c r="B221" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.2">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="222" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A222" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="B222" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.2">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="223" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A223" s="3" t="s">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="B223" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.2">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="224" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A224" s="3" t="s">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="B224" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
     </row>
     <row r="225" spans="1:12" x14ac:dyDescent="0.2">
@@ -4162,7 +4150,7 @@
         <v>55</v>
       </c>
       <c r="B225" t="s">
-        <v>73</v>
+        <v>289</v>
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.2">
@@ -4170,47 +4158,53 @@
         <v>0</v>
       </c>
       <c r="B226" t="s">
-        <v>74</v>
+        <v>214</v>
+      </c>
+      <c r="C226" t="s">
+        <v>146</v>
+      </c>
+      <c r="D226" t="s">
+        <v>143</v>
       </c>
     </row>
     <row r="227" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A227" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="B227" t="s">
-        <v>202</v>
+        <v>215</v>
+      </c>
+      <c r="G227" t="s">
+        <v>216</v>
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A228" s="3" t="s">
-        <v>0</v>
-      </c>
       <c r="B228" t="s">
-        <v>203</v>
+        <v>77</v>
+      </c>
+      <c r="D228" t="s">
+        <v>147</v>
+      </c>
+      <c r="F228" t="s">
+        <v>81</v>
+      </c>
+      <c r="G228" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="229" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A229" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="B229" t="s">
-        <v>75</v>
+        <v>204</v>
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A230" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="B230" t="s">
-        <v>76</v>
+        <v>205</v>
       </c>
     </row>
     <row r="231" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A231" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="B231" t="s">
-        <v>289</v>
+        <v>206</v>
+      </c>
+      <c r="D231" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.2">
@@ -4218,68 +4212,14 @@
         <v>0</v>
       </c>
       <c r="B232" t="s">
-        <v>214</v>
-      </c>
-      <c r="C232" t="s">
-        <v>146</v>
-      </c>
-      <c r="D232" t="s">
-        <v>143</v>
+        <v>207</v>
+      </c>
+      <c r="L232" t="s">
+        <v>209</v>
       </c>
     </row>
     <row r="233" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B233" t="s">
-        <v>215</v>
-      </c>
-      <c r="G233" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="234" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B234" t="s">
-        <v>77</v>
-      </c>
-      <c r="D234" t="s">
-        <v>147</v>
-      </c>
-      <c r="F234" t="s">
-        <v>81</v>
-      </c>
-      <c r="G234" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="235" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B235" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="236" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B236" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="237" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="B237" t="s">
-        <v>206</v>
-      </c>
-      <c r="D237" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="238" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A238" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B238" t="s">
-        <v>207</v>
-      </c>
-      <c r="L238" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="239" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="L239" t="s">
+      <c r="L233" t="s">
         <v>78</v>
       </c>
     </row>
